--- a/exports/elo_time_table.xlsx
+++ b/exports/elo_time_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV168"/>
+  <dimension ref="A1:BF187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,56 @@
       <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Ronan McKinney</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Ryan Healy</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Graham Longhofer</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Hares Ragub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Nic Faulds</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Maria Stalcup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Benjamin Merkel</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Sakeena Saidou</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Harper Willingham</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Z Hayes</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Victoria LastName</t>
         </is>
       </c>
     </row>
@@ -724,6 +774,16 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -784,6 +844,16 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -844,6 +914,16 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -904,6 +984,16 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -964,6 +1054,16 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1024,6 +1124,16 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1084,6 +1194,16 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1144,6 +1264,16 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1204,6 +1334,16 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1264,6 +1404,16 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1324,6 +1474,16 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1384,6 +1544,16 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1444,6 +1614,16 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1504,6 +1684,16 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1560,6 +1750,16 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1616,6 +1816,16 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1672,6 +1882,16 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1728,6 +1948,16 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1784,6 +2014,16 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1840,6 +2080,16 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AU21" t="inlineStr"/>
       <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1896,6 +2146,16 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr"/>
       <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1952,6 +2212,16 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2008,6 +2278,16 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AU24" t="inlineStr"/>
       <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2064,6 +2344,16 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AU25" t="inlineStr"/>
       <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2120,6 +2410,16 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AU26" t="inlineStr"/>
       <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2176,6 +2476,16 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2232,6 +2542,16 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AU28" t="inlineStr"/>
       <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2288,6 +2608,16 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AU29" t="inlineStr"/>
       <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2344,6 +2674,16 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
       <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2400,6 +2740,16 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2456,6 +2806,16 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2512,6 +2872,16 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AU33" t="inlineStr"/>
       <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2568,6 +2938,16 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2624,6 +3004,16 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AU35" t="inlineStr"/>
       <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2680,6 +3070,16 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AU36" t="inlineStr"/>
       <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2736,6 +3136,16 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2792,6 +3202,16 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AU38" t="inlineStr"/>
       <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2848,6 +3268,16 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AU39" t="inlineStr"/>
       <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2904,6 +3334,16 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AU40" t="inlineStr"/>
       <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2960,6 +3400,16 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AU41" t="inlineStr"/>
       <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3016,6 +3466,16 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AU42" t="inlineStr"/>
       <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3072,6 +3532,16 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AU43" t="inlineStr"/>
       <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3128,6 +3598,16 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AU44" t="inlineStr"/>
       <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3188,6 +3668,16 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AU45" t="inlineStr"/>
       <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3248,6 +3738,16 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AU46" t="inlineStr"/>
       <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3308,6 +3808,16 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AU47" t="inlineStr"/>
       <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3368,6 +3878,16 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AU48" t="inlineStr"/>
       <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3428,6 +3948,16 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AU49" t="inlineStr"/>
       <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3488,6 +4018,16 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AU50" t="inlineStr"/>
       <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3548,6 +4088,16 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3608,6 +4158,16 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AU52" t="inlineStr"/>
       <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3668,6 +4228,16 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3728,6 +4298,16 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
+      <c r="BA54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3788,6 +4368,16 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
+      <c r="BA55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3848,6 +4438,16 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AU56" t="inlineStr"/>
       <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -3908,6 +4508,16 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AU57" t="inlineStr"/>
       <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
+      <c r="BA57" t="inlineStr"/>
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3968,6 +4578,16 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AU58" t="inlineStr"/>
       <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
+      <c r="BA58" t="inlineStr"/>
+      <c r="BB58" t="inlineStr"/>
+      <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -4028,6 +4648,16 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AU59" t="inlineStr"/>
       <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
+      <c r="BA59" t="inlineStr"/>
+      <c r="BB59" t="inlineStr"/>
+      <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4088,6 +4718,16 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
+      <c r="BA60" t="inlineStr"/>
+      <c r="BB60" t="inlineStr"/>
+      <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4148,6 +4788,16 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4204,6 +4854,16 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
+      <c r="BA62" t="inlineStr"/>
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4260,6 +4920,16 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AU63" t="inlineStr"/>
       <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
+      <c r="BA63" t="inlineStr"/>
+      <c r="BB63" t="inlineStr"/>
+      <c r="BC63" t="inlineStr"/>
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4316,6 +4986,16 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AU64" t="inlineStr"/>
       <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
+      <c r="BA64" t="inlineStr"/>
+      <c r="BB64" t="inlineStr"/>
+      <c r="BC64" t="inlineStr"/>
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4372,6 +5052,16 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AU65" t="inlineStr"/>
       <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
+      <c r="BA65" t="inlineStr"/>
+      <c r="BB65" t="inlineStr"/>
+      <c r="BC65" t="inlineStr"/>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4428,6 +5118,16 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AU66" t="inlineStr"/>
       <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
+      <c r="BA66" t="inlineStr"/>
+      <c r="BB66" t="inlineStr"/>
+      <c r="BC66" t="inlineStr"/>
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4484,6 +5184,16 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AU67" t="inlineStr"/>
       <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr"/>
+      <c r="BA67" t="inlineStr"/>
+      <c r="BB67" t="inlineStr"/>
+      <c r="BC67" t="inlineStr"/>
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4540,6 +5250,16 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AU68" t="inlineStr"/>
       <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
+      <c r="BA68" t="inlineStr"/>
+      <c r="BB68" t="inlineStr"/>
+      <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4596,6 +5316,16 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AU69" t="inlineStr"/>
       <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
+      <c r="BA69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4652,6 +5382,16 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AU70" t="inlineStr"/>
       <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
+      <c r="BA70" t="inlineStr"/>
+      <c r="BB70" t="inlineStr"/>
+      <c r="BC70" t="inlineStr"/>
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4708,6 +5448,16 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AU71" t="inlineStr"/>
       <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
+      <c r="BA71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4764,6 +5514,16 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AU72" t="inlineStr"/>
       <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
+      <c r="BA72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -4820,6 +5580,16 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AU73" t="inlineStr"/>
       <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
+      <c r="BA73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -4876,6 +5646,16 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr"/>
+      <c r="BA74" t="inlineStr"/>
+      <c r="BB74" t="inlineStr"/>
+      <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="inlineStr"/>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -4932,6 +5712,16 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AU75" t="inlineStr"/>
       <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr"/>
+      <c r="BA75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr"/>
+      <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -4988,6 +5778,16 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AU76" t="inlineStr"/>
       <c r="AV76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr"/>
+      <c r="BA76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr"/>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -5044,6 +5844,16 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AU77" t="inlineStr"/>
       <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr"/>
+      <c r="BA77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr"/>
+      <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="inlineStr"/>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5100,6 +5910,16 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AU78" t="inlineStr"/>
       <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr"/>
+      <c r="BA78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr"/>
+      <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="inlineStr"/>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -5156,6 +5976,16 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AU79" t="inlineStr"/>
       <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr"/>
+      <c r="AX79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr"/>
+      <c r="BA79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr"/>
+      <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr"/>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -5212,6 +6042,16 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AU80" t="inlineStr"/>
       <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -5268,6 +6108,16 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AU81" t="inlineStr"/>
       <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5324,6 +6174,16 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AU82" t="inlineStr"/>
       <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr"/>
+      <c r="BA82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -5380,6 +6240,16 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr"/>
+      <c r="AX83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr"/>
+      <c r="BA83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr"/>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -5436,6 +6306,16 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AU84" t="inlineStr"/>
       <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr"/>
+      <c r="AX84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr"/>
+      <c r="BA84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr"/>
+      <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -5492,6 +6372,16 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AU85" t="inlineStr"/>
       <c r="AV85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr"/>
+      <c r="AX85" t="inlineStr"/>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr"/>
+      <c r="BA85" t="inlineStr"/>
+      <c r="BB85" t="inlineStr"/>
+      <c r="BC85" t="inlineStr"/>
+      <c r="BD85" t="inlineStr"/>
+      <c r="BE85" t="inlineStr"/>
+      <c r="BF85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -5548,6 +6438,16 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AU86" t="inlineStr"/>
       <c r="AV86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr"/>
+      <c r="AX86" t="inlineStr"/>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr"/>
+      <c r="BA86" t="inlineStr"/>
+      <c r="BB86" t="inlineStr"/>
+      <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="inlineStr"/>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -5604,6 +6504,16 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AU87" t="inlineStr"/>
       <c r="AV87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr"/>
+      <c r="AX87" t="inlineStr"/>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr"/>
+      <c r="BA87" t="inlineStr"/>
+      <c r="BB87" t="inlineStr"/>
+      <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="inlineStr"/>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5660,6 +6570,16 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AU88" t="inlineStr"/>
       <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
+      <c r="AX88" t="inlineStr"/>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr"/>
+      <c r="BA88" t="inlineStr"/>
+      <c r="BB88" t="inlineStr"/>
+      <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -5716,6 +6636,16 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AU89" t="inlineStr"/>
       <c r="AV89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr"/>
+      <c r="AX89" t="inlineStr"/>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr"/>
+      <c r="BA89" t="inlineStr"/>
+      <c r="BB89" t="inlineStr"/>
+      <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -5772,6 +6702,16 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AU90" t="inlineStr"/>
       <c r="AV90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr"/>
+      <c r="BA90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr"/>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -5828,6 +6768,16 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AU91" t="inlineStr"/>
       <c r="AV91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr"/>
+      <c r="AX91" t="inlineStr"/>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr"/>
+      <c r="BA91" t="inlineStr"/>
+      <c r="BB91" t="inlineStr"/>
+      <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -5884,6 +6834,16 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AU92" t="inlineStr"/>
       <c r="AV92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr"/>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr"/>
+      <c r="BA92" t="inlineStr"/>
+      <c r="BB92" t="inlineStr"/>
+      <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -5940,6 +6900,16 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AU93" t="inlineStr"/>
       <c r="AV93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr"/>
+      <c r="AX93" t="inlineStr"/>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr"/>
+      <c r="BA93" t="inlineStr"/>
+      <c r="BB93" t="inlineStr"/>
+      <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -5996,6 +6966,16 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AU94" t="inlineStr"/>
       <c r="AV94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr"/>
+      <c r="AX94" t="inlineStr"/>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr"/>
+      <c r="BA94" t="inlineStr"/>
+      <c r="BB94" t="inlineStr"/>
+      <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -6052,6 +7032,16 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AU95" t="inlineStr"/>
       <c r="AV95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr"/>
+      <c r="AX95" t="inlineStr"/>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr"/>
+      <c r="BA95" t="inlineStr"/>
+      <c r="BB95" t="inlineStr"/>
+      <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -6108,6 +7098,16 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AU96" t="inlineStr"/>
       <c r="AV96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr"/>
+      <c r="AX96" t="inlineStr"/>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr"/>
+      <c r="BA96" t="inlineStr"/>
+      <c r="BB96" t="inlineStr"/>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -6164,6 +7164,16 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AU97" t="inlineStr"/>
       <c r="AV97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr"/>
+      <c r="AX97" t="inlineStr"/>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr"/>
+      <c r="BA97" t="inlineStr"/>
+      <c r="BB97" t="inlineStr"/>
+      <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -6220,6 +7230,16 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AU98" t="inlineStr"/>
       <c r="AV98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr"/>
+      <c r="AX98" t="inlineStr"/>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr"/>
+      <c r="BA98" t="inlineStr"/>
+      <c r="BB98" t="inlineStr"/>
+      <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -6280,6 +7300,16 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AU99" t="inlineStr"/>
       <c r="AV99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr"/>
+      <c r="AX99" t="inlineStr"/>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr"/>
+      <c r="BA99" t="inlineStr"/>
+      <c r="BB99" t="inlineStr"/>
+      <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -6340,6 +7370,16 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AU100" t="inlineStr"/>
       <c r="AV100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr"/>
+      <c r="AX100" t="inlineStr"/>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr"/>
+      <c r="BA100" t="inlineStr"/>
+      <c r="BB100" t="inlineStr"/>
+      <c r="BC100" t="inlineStr"/>
+      <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -6400,6 +7440,16 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AU101" t="inlineStr"/>
       <c r="AV101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr"/>
+      <c r="AX101" t="inlineStr"/>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr"/>
+      <c r="BA101" t="inlineStr"/>
+      <c r="BB101" t="inlineStr"/>
+      <c r="BC101" t="inlineStr"/>
+      <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6460,6 +7510,16 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AU102" t="inlineStr"/>
       <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr"/>
+      <c r="BA102" t="inlineStr"/>
+      <c r="BB102" t="inlineStr"/>
+      <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -6520,6 +7580,16 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AU103" t="inlineStr"/>
       <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr"/>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr"/>
+      <c r="BA103" t="inlineStr"/>
+      <c r="BB103" t="inlineStr"/>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -6580,6 +7650,16 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AU104" t="inlineStr"/>
       <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr"/>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr"/>
+      <c r="BA104" t="inlineStr"/>
+      <c r="BB104" t="inlineStr"/>
+      <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -6640,6 +7720,16 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AU105" t="inlineStr"/>
       <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr"/>
+      <c r="BA105" t="inlineStr"/>
+      <c r="BB105" t="inlineStr"/>
+      <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -6700,6 +7790,16 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AU106" t="inlineStr"/>
       <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr"/>
+      <c r="BA106" t="inlineStr"/>
+      <c r="BB106" t="inlineStr"/>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -6760,6 +7860,16 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AU107" t="inlineStr"/>
       <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr"/>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr"/>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -6820,6 +7930,16 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AU108" t="inlineStr"/>
       <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr"/>
+      <c r="BA108" t="inlineStr"/>
+      <c r="BB108" t="inlineStr"/>
+      <c r="BC108" t="inlineStr"/>
+      <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -6880,6 +8000,16 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr"/>
+      <c r="BA109" t="inlineStr"/>
+      <c r="BB109" t="inlineStr"/>
+      <c r="BC109" t="inlineStr"/>
+      <c r="BD109" t="inlineStr"/>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -6940,6 +8070,16 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AU110" t="inlineStr"/>
       <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr"/>
+      <c r="AX110" t="inlineStr"/>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr"/>
+      <c r="BA110" t="inlineStr"/>
+      <c r="BB110" t="inlineStr"/>
+      <c r="BC110" t="inlineStr"/>
+      <c r="BD110" t="inlineStr"/>
+      <c r="BE110" t="inlineStr"/>
+      <c r="BF110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -7000,6 +8140,16 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AU111" t="inlineStr"/>
       <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr"/>
+      <c r="AX111" t="inlineStr"/>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr"/>
+      <c r="BA111" t="inlineStr"/>
+      <c r="BB111" t="inlineStr"/>
+      <c r="BC111" t="inlineStr"/>
+      <c r="BD111" t="inlineStr"/>
+      <c r="BE111" t="inlineStr"/>
+      <c r="BF111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -7060,6 +8210,16 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AU112" t="inlineStr"/>
       <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr"/>
+      <c r="BA112" t="inlineStr"/>
+      <c r="BB112" t="inlineStr"/>
+      <c r="BC112" t="inlineStr"/>
+      <c r="BD112" t="inlineStr"/>
+      <c r="BE112" t="inlineStr"/>
+      <c r="BF112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -7116,6 +8276,16 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AU113" t="inlineStr"/>
       <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr"/>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr"/>
+      <c r="BA113" t="inlineStr"/>
+      <c r="BB113" t="inlineStr"/>
+      <c r="BC113" t="inlineStr"/>
+      <c r="BD113" t="inlineStr"/>
+      <c r="BE113" t="inlineStr"/>
+      <c r="BF113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -7172,6 +8342,16 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AU114" t="inlineStr"/>
       <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr"/>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr"/>
+      <c r="BA114" t="inlineStr"/>
+      <c r="BB114" t="inlineStr"/>
+      <c r="BC114" t="inlineStr"/>
+      <c r="BD114" t="inlineStr"/>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -7228,6 +8408,16 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AU115" t="inlineStr"/>
       <c r="AV115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr"/>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr"/>
+      <c r="BA115" t="inlineStr"/>
+      <c r="BB115" t="inlineStr"/>
+      <c r="BC115" t="inlineStr"/>
+      <c r="BD115" t="inlineStr"/>
+      <c r="BE115" t="inlineStr"/>
+      <c r="BF115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -7284,6 +8474,16 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AU116" t="inlineStr"/>
       <c r="AV116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr"/>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr"/>
+      <c r="BA116" t="inlineStr"/>
+      <c r="BB116" t="inlineStr"/>
+      <c r="BC116" t="inlineStr"/>
+      <c r="BD116" t="inlineStr"/>
+      <c r="BE116" t="inlineStr"/>
+      <c r="BF116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -7340,6 +8540,16 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AU117" t="inlineStr"/>
       <c r="AV117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr"/>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr"/>
+      <c r="BA117" t="inlineStr"/>
+      <c r="BB117" t="inlineStr"/>
+      <c r="BC117" t="inlineStr"/>
+      <c r="BD117" t="inlineStr"/>
+      <c r="BE117" t="inlineStr"/>
+      <c r="BF117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -7396,6 +8606,16 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AU118" t="inlineStr"/>
       <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr"/>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7452,6 +8672,16 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AU119" t="inlineStr"/>
       <c r="AV119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr"/>
+      <c r="AX119" t="inlineStr"/>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr"/>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -7508,6 +8738,16 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AU120" t="inlineStr"/>
       <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr"/>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr"/>
+      <c r="BA120" t="inlineStr"/>
+      <c r="BB120" t="inlineStr"/>
+      <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="inlineStr"/>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -7564,6 +8804,16 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AU121" t="inlineStr"/>
       <c r="AV121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr"/>
+      <c r="AX121" t="inlineStr"/>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr"/>
+      <c r="BA121" t="inlineStr"/>
+      <c r="BB121" t="inlineStr"/>
+      <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -7620,6 +8870,16 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr"/>
+      <c r="AX122" t="inlineStr"/>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr"/>
+      <c r="BA122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr"/>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -7676,6 +8936,16 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AU123" t="inlineStr"/>
       <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr"/>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr"/>
+      <c r="BA123" t="inlineStr"/>
+      <c r="BB123" t="inlineStr"/>
+      <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -7732,6 +9002,16 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AU124" t="inlineStr"/>
       <c r="AV124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr"/>
+      <c r="BA124" t="inlineStr"/>
+      <c r="BB124" t="inlineStr"/>
+      <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="inlineStr"/>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -7788,6 +9068,16 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AU125" t="inlineStr"/>
       <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr"/>
+      <c r="BA125" t="inlineStr"/>
+      <c r="BB125" t="inlineStr"/>
+      <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -7844,6 +9134,16 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AU126" t="inlineStr"/>
       <c r="AV126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr"/>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr"/>
+      <c r="BA126" t="inlineStr"/>
+      <c r="BB126" t="inlineStr"/>
+      <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -7900,6 +9200,16 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AU127" t="inlineStr"/>
       <c r="AV127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr"/>
+      <c r="AX127" t="inlineStr"/>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr"/>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -7956,6 +9266,16 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AU128" t="inlineStr"/>
       <c r="AV128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr"/>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr"/>
+      <c r="BA128" t="inlineStr"/>
+      <c r="BB128" t="inlineStr"/>
+      <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -8012,6 +9332,16 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AU129" t="inlineStr"/>
       <c r="AV129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr"/>
+      <c r="AX129" t="inlineStr"/>
+      <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr"/>
+      <c r="BA129" t="inlineStr"/>
+      <c r="BB129" t="inlineStr"/>
+      <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -8068,6 +9398,16 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AU130" t="inlineStr"/>
       <c r="AV130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr"/>
+      <c r="AX130" t="inlineStr"/>
+      <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr"/>
+      <c r="BA130" t="inlineStr"/>
+      <c r="BB130" t="inlineStr"/>
+      <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -8128,6 +9468,16 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr"/>
       <c r="AV131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr"/>
+      <c r="AX131" t="inlineStr"/>
+      <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr"/>
+      <c r="BA131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr"/>
+      <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -8188,6 +9538,16 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AU132" t="inlineStr"/>
       <c r="AV132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr"/>
+      <c r="AX132" t="inlineStr"/>
+      <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr"/>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -8248,6 +9608,16 @@
       </c>
       <c r="AU133" t="inlineStr"/>
       <c r="AV133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr"/>
+      <c r="AX133" t="inlineStr"/>
+      <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr"/>
+      <c r="BA133" t="inlineStr"/>
+      <c r="BB133" t="inlineStr"/>
+      <c r="BC133" t="inlineStr"/>
+      <c r="BD133" t="inlineStr"/>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -8308,6 +9678,16 @@
       </c>
       <c r="AU134" t="inlineStr"/>
       <c r="AV134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr"/>
+      <c r="AX134" t="inlineStr"/>
+      <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr"/>
+      <c r="BA134" t="inlineStr"/>
+      <c r="BB134" t="inlineStr"/>
+      <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -8368,6 +9748,16 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AU135" t="inlineStr"/>
       <c r="AV135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr"/>
+      <c r="AX135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr"/>
+      <c r="BA135" t="inlineStr"/>
+      <c r="BB135" t="inlineStr"/>
+      <c r="BC135" t="inlineStr"/>
+      <c r="BD135" t="inlineStr"/>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -8428,6 +9818,16 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AU136" t="inlineStr"/>
       <c r="AV136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr"/>
+      <c r="AX136" t="inlineStr"/>
+      <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr"/>
+      <c r="BA136" t="inlineStr"/>
+      <c r="BB136" t="inlineStr"/>
+      <c r="BC136" t="inlineStr"/>
+      <c r="BD136" t="inlineStr"/>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -8488,6 +9888,16 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AU137" t="inlineStr"/>
       <c r="AV137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr"/>
+      <c r="AX137" t="inlineStr"/>
+      <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr"/>
+      <c r="BA137" t="inlineStr"/>
+      <c r="BB137" t="inlineStr"/>
+      <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -8548,6 +9958,16 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AU138" t="inlineStr"/>
       <c r="AV138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr"/>
+      <c r="AX138" t="inlineStr"/>
+      <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr"/>
+      <c r="BA138" t="inlineStr"/>
+      <c r="BB138" t="inlineStr"/>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -8608,6 +10028,16 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AU139" t="inlineStr"/>
       <c r="AV139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr"/>
+      <c r="AX139" t="inlineStr"/>
+      <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr"/>
+      <c r="BA139" t="inlineStr"/>
+      <c r="BB139" t="inlineStr"/>
+      <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -8668,6 +10098,16 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AU140" t="inlineStr"/>
       <c r="AV140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr"/>
+      <c r="AX140" t="inlineStr"/>
+      <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr"/>
+      <c r="BA140" t="inlineStr"/>
+      <c r="BB140" t="inlineStr"/>
+      <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -8728,6 +10168,16 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AU141" t="inlineStr"/>
       <c r="AV141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr"/>
+      <c r="AX141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr"/>
+      <c r="BA141" t="inlineStr"/>
+      <c r="BB141" t="inlineStr"/>
+      <c r="BC141" t="inlineStr"/>
+      <c r="BD141" t="inlineStr"/>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -8788,6 +10238,16 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AU142" t="inlineStr"/>
       <c r="AV142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr"/>
+      <c r="AX142" t="inlineStr"/>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr"/>
+      <c r="BA142" t="inlineStr"/>
+      <c r="BB142" t="inlineStr"/>
+      <c r="BC142" t="inlineStr"/>
+      <c r="BD142" t="inlineStr"/>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -8844,6 +10304,16 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AU143" t="inlineStr"/>
       <c r="AV143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr"/>
+      <c r="AX143" t="inlineStr"/>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr"/>
+      <c r="BA143" t="inlineStr"/>
+      <c r="BB143" t="inlineStr"/>
+      <c r="BC143" t="inlineStr"/>
+      <c r="BD143" t="inlineStr"/>
+      <c r="BE143" t="inlineStr"/>
+      <c r="BF143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -8900,6 +10370,16 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AU144" t="inlineStr"/>
       <c r="AV144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr"/>
+      <c r="AX144" t="inlineStr"/>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr"/>
+      <c r="BA144" t="inlineStr"/>
+      <c r="BB144" t="inlineStr"/>
+      <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -8956,6 +10436,16 @@
       <c r="AV145" t="n">
         <v>1209.521702761487</v>
       </c>
+      <c r="AW145" t="inlineStr"/>
+      <c r="AX145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr"/>
+      <c r="BA145" t="inlineStr"/>
+      <c r="BB145" t="inlineStr"/>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -9012,6 +10502,16 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AU146" t="inlineStr"/>
       <c r="AV146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr"/>
+      <c r="AX146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr"/>
+      <c r="BA146" t="inlineStr"/>
+      <c r="BB146" t="inlineStr"/>
+      <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -9068,6 +10568,16 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AU147" t="inlineStr"/>
       <c r="AV147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr"/>
+      <c r="AX147" t="inlineStr"/>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr"/>
+      <c r="BA147" t="inlineStr"/>
+      <c r="BB147" t="inlineStr"/>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="inlineStr"/>
+      <c r="BF147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -9124,6 +10634,16 @@
         <v>1188.335234184947</v>
       </c>
       <c r="AV148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr"/>
+      <c r="AX148" t="inlineStr"/>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr"/>
+      <c r="BA148" t="inlineStr"/>
+      <c r="BB148" t="inlineStr"/>
+      <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="inlineStr"/>
+      <c r="BF148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -9180,6 +10700,16 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AU149" t="inlineStr"/>
       <c r="AV149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr"/>
+      <c r="AX149" t="inlineStr"/>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr"/>
+      <c r="BA149" t="inlineStr"/>
+      <c r="BB149" t="inlineStr"/>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -9236,6 +10766,16 @@
         <v>1223.284751675888</v>
       </c>
       <c r="AV150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr"/>
+      <c r="AX150" t="inlineStr"/>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr"/>
+      <c r="BA150" t="inlineStr"/>
+      <c r="BB150" t="inlineStr"/>
+      <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="inlineStr"/>
+      <c r="BF150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -9292,6 +10832,16 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AU151" t="inlineStr"/>
       <c r="AV151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr"/>
+      <c r="AX151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr"/>
+      <c r="BA151" t="inlineStr"/>
+      <c r="BB151" t="inlineStr"/>
+      <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="inlineStr"/>
+      <c r="BF151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -9348,6 +10898,16 @@
       <c r="AV152" t="n">
         <v>1197.916106876707</v>
       </c>
+      <c r="AW152" t="inlineStr"/>
+      <c r="AX152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr"/>
+      <c r="BA152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr"/>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -9404,6 +10964,16 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AU153" t="inlineStr"/>
       <c r="AV153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr"/>
+      <c r="AX153" t="inlineStr"/>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr"/>
+      <c r="BA153" t="inlineStr"/>
+      <c r="BB153" t="inlineStr"/>
+      <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="inlineStr"/>
+      <c r="BF153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -9460,6 +11030,16 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr"/>
       <c r="AV154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr"/>
+      <c r="AX154" t="inlineStr"/>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr"/>
+      <c r="BA154" t="inlineStr"/>
+      <c r="BB154" t="inlineStr"/>
+      <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="inlineStr"/>
+      <c r="BF154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -9516,6 +11096,16 @@
         <v>1237.516385165518</v>
       </c>
       <c r="AV155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr"/>
+      <c r="AX155" t="inlineStr"/>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr"/>
+      <c r="BA155" t="inlineStr"/>
+      <c r="BB155" t="inlineStr"/>
+      <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="inlineStr"/>
+      <c r="BF155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -9572,6 +11162,16 @@
       <c r="AV156" t="n">
         <v>1172.998834244298</v>
       </c>
+      <c r="AW156" t="inlineStr"/>
+      <c r="AX156" t="inlineStr"/>
+      <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr"/>
+      <c r="BA156" t="inlineStr"/>
+      <c r="BB156" t="inlineStr"/>
+      <c r="BC156" t="inlineStr"/>
+      <c r="BD156" t="inlineStr"/>
+      <c r="BE156" t="inlineStr"/>
+      <c r="BF156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -9628,6 +11228,16 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AU157" t="inlineStr"/>
       <c r="AV157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr"/>
+      <c r="AX157" t="inlineStr"/>
+      <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr"/>
+      <c r="BA157" t="inlineStr"/>
+      <c r="BB157" t="inlineStr"/>
+      <c r="BC157" t="inlineStr"/>
+      <c r="BD157" t="inlineStr"/>
+      <c r="BE157" t="inlineStr"/>
+      <c r="BF157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -9684,6 +11294,16 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AU158" t="inlineStr"/>
       <c r="AV158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr"/>
+      <c r="AX158" t="inlineStr"/>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr"/>
+      <c r="BA158" t="inlineStr"/>
+      <c r="BB158" t="inlineStr"/>
+      <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="inlineStr"/>
+      <c r="BF158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -9740,6 +11360,16 @@
         <v>1211.683485439216</v>
       </c>
       <c r="AV159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr"/>
+      <c r="AX159" t="inlineStr"/>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr"/>
+      <c r="BA159" t="inlineStr"/>
+      <c r="BB159" t="inlineStr"/>
+      <c r="BC159" t="inlineStr"/>
+      <c r="BD159" t="inlineStr"/>
+      <c r="BE159" t="inlineStr"/>
+      <c r="BF159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -9796,6 +11426,16 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AU160" t="inlineStr"/>
       <c r="AV160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr"/>
+      <c r="AX160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr"/>
+      <c r="BA160" t="inlineStr"/>
+      <c r="BB160" t="inlineStr"/>
+      <c r="BC160" t="inlineStr"/>
+      <c r="BD160" t="inlineStr"/>
+      <c r="BE160" t="inlineStr"/>
+      <c r="BF160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -9852,6 +11492,16 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AU161" t="inlineStr"/>
       <c r="AV161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr"/>
+      <c r="AX161" t="inlineStr"/>
+      <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr"/>
+      <c r="BA161" t="inlineStr"/>
+      <c r="BB161" t="inlineStr"/>
+      <c r="BC161" t="inlineStr"/>
+      <c r="BD161" t="inlineStr"/>
+      <c r="BE161" t="inlineStr"/>
+      <c r="BF161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -9908,6 +11558,16 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AU162" t="inlineStr"/>
       <c r="AV162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr"/>
+      <c r="AX162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr"/>
+      <c r="BA162" t="inlineStr"/>
+      <c r="BB162" t="inlineStr"/>
+      <c r="BC162" t="inlineStr"/>
+      <c r="BD162" t="inlineStr"/>
+      <c r="BE162" t="inlineStr"/>
+      <c r="BF162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -9964,6 +11624,16 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AU163" t="inlineStr"/>
       <c r="AV163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr"/>
+      <c r="AX163" t="inlineStr"/>
+      <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr"/>
+      <c r="BA163" t="inlineStr"/>
+      <c r="BB163" t="inlineStr"/>
+      <c r="BC163" t="inlineStr"/>
+      <c r="BD163" t="inlineStr"/>
+      <c r="BE163" t="inlineStr"/>
+      <c r="BF163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -10020,6 +11690,16 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AU164" t="inlineStr"/>
       <c r="AV164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr"/>
+      <c r="AX164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr"/>
+      <c r="BA164" t="inlineStr"/>
+      <c r="BB164" t="inlineStr"/>
+      <c r="BC164" t="inlineStr"/>
+      <c r="BD164" t="inlineStr"/>
+      <c r="BE164" t="inlineStr"/>
+      <c r="BF164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -10076,6 +11756,16 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AU165" t="inlineStr"/>
       <c r="AV165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr"/>
+      <c r="AX165" t="inlineStr"/>
+      <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr"/>
+      <c r="BA165" t="inlineStr"/>
+      <c r="BB165" t="inlineStr"/>
+      <c r="BC165" t="inlineStr"/>
+      <c r="BD165" t="inlineStr"/>
+      <c r="BE165" t="inlineStr"/>
+      <c r="BF165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -10132,6 +11822,16 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AU166" t="inlineStr"/>
       <c r="AV166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr"/>
+      <c r="AX166" t="inlineStr"/>
+      <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr"/>
+      <c r="BA166" t="inlineStr"/>
+      <c r="BB166" t="inlineStr"/>
+      <c r="BC166" t="inlineStr"/>
+      <c r="BD166" t="inlineStr"/>
+      <c r="BE166" t="inlineStr"/>
+      <c r="BF166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -10188,6 +11888,16 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AU167" t="inlineStr"/>
       <c r="AV167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr"/>
+      <c r="AX167" t="inlineStr"/>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr"/>
+      <c r="BA167" t="inlineStr"/>
+      <c r="BB167" t="inlineStr"/>
+      <c r="BC167" t="inlineStr"/>
+      <c r="BD167" t="inlineStr"/>
+      <c r="BE167" t="inlineStr"/>
+      <c r="BF167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -10244,6 +11954,1346 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AU168" t="inlineStr"/>
       <c r="AV168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr"/>
+      <c r="AX168" t="inlineStr"/>
+      <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr"/>
+      <c r="BA168" t="inlineStr"/>
+      <c r="BB168" t="inlineStr"/>
+      <c r="BC168" t="inlineStr"/>
+      <c r="BD168" t="inlineStr"/>
+      <c r="BE168" t="inlineStr"/>
+      <c r="BF168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="n">
+        <v>1220.8805187809</v>
+      </c>
+      <c r="AI169" t="inlineStr"/>
+      <c r="AJ169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr"/>
+      <c r="AL169" t="inlineStr"/>
+      <c r="AM169" t="inlineStr"/>
+      <c r="AN169" t="inlineStr"/>
+      <c r="AO169" t="inlineStr"/>
+      <c r="AP169" t="inlineStr"/>
+      <c r="AQ169" t="inlineStr"/>
+      <c r="AR169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AU169" t="inlineStr"/>
+      <c r="AV169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr"/>
+      <c r="AX169" t="inlineStr"/>
+      <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr"/>
+      <c r="BA169" t="inlineStr"/>
+      <c r="BB169" t="n">
+        <v>1186.941462008188</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>1213.058537991812</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>1213.058537991812</v>
+      </c>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="n">
+        <v>1115.286028249105</v>
+      </c>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
+      <c r="AJ170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr"/>
+      <c r="AL170" t="n">
+        <v>1239.90714700855</v>
+      </c>
+      <c r="AM170" t="inlineStr"/>
+      <c r="AN170" t="inlineStr"/>
+      <c r="AO170" t="inlineStr"/>
+      <c r="AP170" t="inlineStr"/>
+      <c r="AQ170" t="inlineStr"/>
+      <c r="AR170" t="inlineStr"/>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AU170" t="inlineStr"/>
+      <c r="AV170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr"/>
+      <c r="AX170" t="inlineStr"/>
+      <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr"/>
+      <c r="BA170" t="n">
+        <v>1208.655214665193</v>
+      </c>
+      <c r="BB170" t="inlineStr"/>
+      <c r="BC170" t="inlineStr"/>
+      <c r="BD170" t="inlineStr"/>
+      <c r="BE170" t="inlineStr"/>
+      <c r="BF170" t="n">
+        <v>1191.344785334807</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="n">
+        <v>1229.499096581331</v>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="n">
+        <v>1002.41151903124</v>
+      </c>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="inlineStr"/>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr"/>
+      <c r="AJ171" t="inlineStr"/>
+      <c r="AK171" t="inlineStr"/>
+      <c r="AL171" t="inlineStr"/>
+      <c r="AM171" t="inlineStr"/>
+      <c r="AN171" t="inlineStr"/>
+      <c r="AO171" t="inlineStr"/>
+      <c r="AP171" t="inlineStr"/>
+      <c r="AQ171" t="inlineStr"/>
+      <c r="AR171" t="inlineStr"/>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AU171" t="n">
+        <v>1242.147204052574</v>
+      </c>
+      <c r="AV171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr"/>
+      <c r="AX171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="n">
+        <v>1169.536281386642</v>
+      </c>
+      <c r="BA171" t="inlineStr"/>
+      <c r="BB171" t="inlineStr"/>
+      <c r="BC171" t="inlineStr"/>
+      <c r="BD171" t="inlineStr"/>
+      <c r="BE171" t="inlineStr"/>
+      <c r="BF171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="n">
+        <v>1206.640272738997</v>
+      </c>
+      <c r="V172" t="inlineStr"/>
+      <c r="W172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
+      <c r="AE172" t="inlineStr"/>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr"/>
+      <c r="AJ172" t="inlineStr"/>
+      <c r="AK172" t="inlineStr"/>
+      <c r="AL172" t="inlineStr"/>
+      <c r="AM172" t="inlineStr"/>
+      <c r="AN172" t="inlineStr"/>
+      <c r="AO172" t="inlineStr"/>
+      <c r="AP172" t="inlineStr"/>
+      <c r="AQ172" t="inlineStr"/>
+      <c r="AR172" t="n">
+        <v>1233.611989496431</v>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AU172" t="inlineStr"/>
+      <c r="AV172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr"/>
+      <c r="AX172" t="n">
+        <v>1137.348317947298</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>1137.348317947298</v>
+      </c>
+      <c r="AZ172" t="inlineStr"/>
+      <c r="BA172" t="inlineStr"/>
+      <c r="BB172" t="inlineStr"/>
+      <c r="BC172" t="inlineStr"/>
+      <c r="BD172" t="inlineStr"/>
+      <c r="BE172" t="inlineStr"/>
+      <c r="BF172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="inlineStr"/>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr"/>
+      <c r="AJ173" t="inlineStr"/>
+      <c r="AK173" t="inlineStr"/>
+      <c r="AL173" t="inlineStr"/>
+      <c r="AM173" t="inlineStr"/>
+      <c r="AN173" t="n">
+        <v>1292.253633251383</v>
+      </c>
+      <c r="AO173" t="inlineStr"/>
+      <c r="AP173" t="inlineStr"/>
+      <c r="AQ173" t="inlineStr"/>
+      <c r="AR173" t="inlineStr"/>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AU173" t="inlineStr"/>
+      <c r="AV173" t="inlineStr"/>
+      <c r="AW173" t="n">
+        <v>1247.41609107546</v>
+      </c>
+      <c r="AX173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr"/>
+      <c r="BA173" t="inlineStr"/>
+      <c r="BB173" t="inlineStr"/>
+      <c r="BC173" t="n">
+        <v>1165.642446916352</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1165.642446916352</v>
+      </c>
+      <c r="BE173" t="inlineStr"/>
+      <c r="BF173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+      <c r="AE174" t="inlineStr"/>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr"/>
+      <c r="AJ174" t="inlineStr"/>
+      <c r="AK174" t="inlineStr"/>
+      <c r="AL174" t="n">
+        <v>1227.3543958276</v>
+      </c>
+      <c r="AM174" t="inlineStr"/>
+      <c r="AN174" t="inlineStr"/>
+      <c r="AO174" t="inlineStr"/>
+      <c r="AP174" t="n">
+        <v>1241.640329831393</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1214.306044096493</v>
+      </c>
+      <c r="AR174" t="inlineStr"/>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AU174" t="inlineStr"/>
+      <c r="AV174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr"/>
+      <c r="AX174" t="inlineStr"/>
+      <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr"/>
+      <c r="BA174" t="n">
+        <v>1196.102463484243</v>
+      </c>
+      <c r="BB174" t="inlineStr"/>
+      <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="n">
+        <v>996.6668171463823</v>
+      </c>
+      <c r="W175" t="inlineStr"/>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
+      <c r="AJ175" t="inlineStr"/>
+      <c r="AK175" t="inlineStr"/>
+      <c r="AL175" t="inlineStr"/>
+      <c r="AM175" t="inlineStr"/>
+      <c r="AN175" t="inlineStr"/>
+      <c r="AO175" t="inlineStr"/>
+      <c r="AP175" t="inlineStr"/>
+      <c r="AQ175" t="inlineStr"/>
+      <c r="AR175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AU175" t="inlineStr"/>
+      <c r="AV175" t="n">
+        <v>1178.743536129156</v>
+      </c>
+      <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr"/>
+      <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="n">
+        <v>1163.791579501785</v>
+      </c>
+      <c r="BA175" t="inlineStr"/>
+      <c r="BB175" t="inlineStr"/>
+      <c r="BC175" t="inlineStr"/>
+      <c r="BD175" t="inlineStr"/>
+      <c r="BE175" t="n">
+        <v>1205.744701884857</v>
+      </c>
+      <c r="BF175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="inlineStr"/>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="n">
+        <v>1228.732720808564</v>
+      </c>
+      <c r="AI176" t="inlineStr"/>
+      <c r="AJ176" t="inlineStr"/>
+      <c r="AK176" t="inlineStr"/>
+      <c r="AL176" t="inlineStr"/>
+      <c r="AM176" t="inlineStr"/>
+      <c r="AN176" t="inlineStr"/>
+      <c r="AO176" t="inlineStr"/>
+      <c r="AP176" t="inlineStr"/>
+      <c r="AQ176" t="inlineStr"/>
+      <c r="AR176" t="inlineStr"/>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AU176" t="inlineStr"/>
+      <c r="AV176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="n">
+        <v>1129.496115919635</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>1129.496115919635</v>
+      </c>
+      <c r="AZ176" t="inlineStr"/>
+      <c r="BA176" t="inlineStr"/>
+      <c r="BB176" t="n">
+        <v>1194.793664035851</v>
+      </c>
+      <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="inlineStr"/>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
+      <c r="AJ177" t="inlineStr"/>
+      <c r="AK177" t="inlineStr"/>
+      <c r="AL177" t="inlineStr"/>
+      <c r="AM177" t="inlineStr"/>
+      <c r="AN177" t="inlineStr"/>
+      <c r="AO177" t="inlineStr"/>
+      <c r="AP177" t="inlineStr"/>
+      <c r="AQ177" t="inlineStr"/>
+      <c r="AR177" t="inlineStr"/>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AU177" t="inlineStr"/>
+      <c r="AV177" t="n">
+        <v>1189.084331268726</v>
+      </c>
+      <c r="AW177" t="inlineStr"/>
+      <c r="AX177" t="inlineStr"/>
+      <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr"/>
+      <c r="BA177" t="inlineStr"/>
+      <c r="BB177" t="inlineStr"/>
+      <c r="BC177" t="n">
+        <v>1155.301651776782</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1155.301651776782</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>1216.085497024427</v>
+      </c>
+      <c r="BF177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="inlineStr"/>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr"/>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
+      <c r="AE178" t="inlineStr"/>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="n">
+        <v>1240.730552194355</v>
+      </c>
+      <c r="AI178" t="inlineStr"/>
+      <c r="AJ178" t="inlineStr"/>
+      <c r="AK178" t="inlineStr"/>
+      <c r="AL178" t="n">
+        <v>1215.356564441809</v>
+      </c>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr"/>
+      <c r="AO178" t="inlineStr"/>
+      <c r="AP178" t="inlineStr"/>
+      <c r="AQ178" t="inlineStr"/>
+      <c r="AR178" t="inlineStr"/>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AU178" t="inlineStr"/>
+      <c r="AV178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr"/>
+      <c r="BA178" t="n">
+        <v>1184.104632098452</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>1206.791495421642</v>
+      </c>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="n">
+        <v>1171.620243599561</v>
+      </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="inlineStr"/>
+      <c r="X179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr"/>
+      <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
+      <c r="AE179" t="inlineStr"/>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr"/>
+      <c r="AJ179" t="inlineStr"/>
+      <c r="AK179" t="inlineStr"/>
+      <c r="AL179" t="inlineStr"/>
+      <c r="AM179" t="inlineStr"/>
+      <c r="AN179" t="n">
+        <v>1350.132486233152</v>
+      </c>
+      <c r="AO179" t="inlineStr"/>
+      <c r="AP179" t="inlineStr"/>
+      <c r="AQ179" t="inlineStr"/>
+      <c r="AR179" t="inlineStr"/>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AU179" t="n">
+        <v>1184.268351070805</v>
+      </c>
+      <c r="AV179" t="inlineStr"/>
+      <c r="AW179" t="n">
+        <v>1305.29494405723</v>
+      </c>
+      <c r="AX179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr"/>
+      <c r="BA179" t="inlineStr"/>
+      <c r="BB179" t="inlineStr"/>
+      <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="n">
+        <v>1195.12979001344</v>
+      </c>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
+      <c r="AE180" t="inlineStr"/>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr"/>
+      <c r="AJ180" t="inlineStr"/>
+      <c r="AK180" t="inlineStr"/>
+      <c r="AL180" t="inlineStr"/>
+      <c r="AM180" t="inlineStr"/>
+      <c r="AN180" t="inlineStr"/>
+      <c r="AO180" t="inlineStr"/>
+      <c r="AP180" t="n">
+        <v>1253.15081255695</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1225.816526822049</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1222.101506770874</v>
+      </c>
+      <c r="AS180" t="inlineStr"/>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AU180" t="inlineStr"/>
+      <c r="AV180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr"/>
+      <c r="AX180" t="inlineStr"/>
+      <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr"/>
+      <c r="BA180" t="inlineStr"/>
+      <c r="BB180" t="inlineStr"/>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="n">
+        <v>1186.476939298028</v>
+      </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr"/>
+      <c r="Y181" t="inlineStr"/>
+      <c r="Z181" t="inlineStr"/>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr"/>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="n">
+        <v>1225.873856495888</v>
+      </c>
+      <c r="AI181" t="inlineStr"/>
+      <c r="AJ181" t="inlineStr"/>
+      <c r="AK181" t="inlineStr"/>
+      <c r="AL181" t="inlineStr"/>
+      <c r="AM181" t="inlineStr"/>
+      <c r="AN181" t="inlineStr"/>
+      <c r="AO181" t="inlineStr"/>
+      <c r="AP181" t="inlineStr"/>
+      <c r="AQ181" t="inlineStr"/>
+      <c r="AR181" t="inlineStr"/>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AU181" t="n">
+        <v>1199.125046769272</v>
+      </c>
+      <c r="AV181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr"/>
+      <c r="AX181" t="inlineStr"/>
+      <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr"/>
+      <c r="BA181" t="inlineStr"/>
+      <c r="BB181" t="n">
+        <v>1191.934799723175</v>
+      </c>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="n">
+        <v>1182.753576657847</v>
+      </c>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
+      <c r="Z182" t="inlineStr"/>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
+      <c r="AE182" t="inlineStr"/>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
+      <c r="AJ182" t="inlineStr"/>
+      <c r="AK182" t="inlineStr"/>
+      <c r="AL182" t="inlineStr"/>
+      <c r="AM182" t="inlineStr"/>
+      <c r="AN182" t="inlineStr"/>
+      <c r="AO182" t="inlineStr"/>
+      <c r="AP182" t="inlineStr"/>
+      <c r="AQ182" t="inlineStr"/>
+      <c r="AR182" t="n">
+        <v>1209.72529341528</v>
+      </c>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AU182" t="inlineStr"/>
+      <c r="AV182" t="n">
+        <v>1201.460544624319</v>
+      </c>
+      <c r="AW182" t="inlineStr"/>
+      <c r="AX182" t="inlineStr"/>
+      <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr"/>
+      <c r="BA182" t="inlineStr"/>
+      <c r="BB182" t="inlineStr"/>
+      <c r="BC182" t="inlineStr"/>
+      <c r="BD182" t="inlineStr"/>
+      <c r="BE182" t="n">
+        <v>1228.461710380021</v>
+      </c>
+      <c r="BF182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="n">
+        <v>1235.859190571467</v>
+      </c>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
+      <c r="AE183" t="inlineStr"/>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr"/>
+      <c r="AJ183" t="inlineStr"/>
+      <c r="AK183" t="inlineStr"/>
+      <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr"/>
+      <c r="AO183" t="inlineStr"/>
+      <c r="AP183" t="inlineStr"/>
+      <c r="AQ183" t="inlineStr"/>
+      <c r="AR183" t="inlineStr"/>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AU183" t="n">
+        <v>1248.50729804271</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>1152.078293350881</v>
+      </c>
+      <c r="AW183" t="inlineStr"/>
+      <c r="AX183" t="inlineStr"/>
+      <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr"/>
+      <c r="BA183" t="inlineStr"/>
+      <c r="BB183" t="inlineStr"/>
+      <c r="BC183" t="inlineStr"/>
+      <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="n">
+        <v>1179.079459106583</v>
+      </c>
+      <c r="BF183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr"/>
+      <c r="AJ184" t="inlineStr"/>
+      <c r="AK184" t="inlineStr"/>
+      <c r="AL184" t="inlineStr"/>
+      <c r="AM184" t="inlineStr"/>
+      <c r="AN184" t="n">
+        <v>1356.639106364001</v>
+      </c>
+      <c r="AO184" t="inlineStr"/>
+      <c r="AP184" t="n">
+        <v>1246.644192426101</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1219.3099066912</v>
+      </c>
+      <c r="AR184" t="inlineStr"/>
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AU184" t="inlineStr"/>
+      <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="n">
+        <v>1311.801564188079</v>
+      </c>
+      <c r="AX184" t="inlineStr"/>
+      <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr"/>
+      <c r="BA184" t="inlineStr"/>
+      <c r="BB184" t="inlineStr"/>
+      <c r="BC184" t="inlineStr"/>
+      <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="n">
+        <v>1247.28489043744</v>
+      </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr"/>
+      <c r="AJ185" t="inlineStr"/>
+      <c r="AK185" t="inlineStr"/>
+      <c r="AL185" t="inlineStr"/>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr"/>
+      <c r="AO185" t="inlineStr"/>
+      <c r="AP185" t="n">
+        <v>1235.218492560128</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1207.884206825227</v>
+      </c>
+      <c r="AR185" t="inlineStr"/>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AU185" t="n">
+        <v>1259.932997908684</v>
+      </c>
+      <c r="AV185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr"/>
+      <c r="AX185" t="inlineStr"/>
+      <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr"/>
+      <c r="BA185" t="inlineStr"/>
+      <c r="BB185" t="inlineStr"/>
+      <c r="BC185" t="inlineStr"/>
+      <c r="BD185" t="inlineStr"/>
+      <c r="BE185" t="inlineStr"/>
+      <c r="BF185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="n">
+        <v>1288.305529380862</v>
+      </c>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr"/>
+      <c r="AJ186" t="inlineStr"/>
+      <c r="AK186" t="inlineStr"/>
+      <c r="AL186" t="inlineStr"/>
+      <c r="AM186" t="inlineStr"/>
+      <c r="AN186" t="n">
+        <v>1315.618467420579</v>
+      </c>
+      <c r="AO186" t="inlineStr"/>
+      <c r="AP186" t="inlineStr"/>
+      <c r="AQ186" t="inlineStr"/>
+      <c r="AR186" t="inlineStr"/>
+      <c r="AS186" t="inlineStr"/>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AU186" t="n">
+        <v>1300.953636852106</v>
+      </c>
+      <c r="AV186" t="inlineStr"/>
+      <c r="AW186" t="n">
+        <v>1270.780925244656</v>
+      </c>
+      <c r="AX186" t="inlineStr"/>
+      <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr"/>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="n">
+        <v>1252.216328447152</v>
+      </c>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr"/>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="inlineStr"/>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
+      <c r="AJ187" t="inlineStr"/>
+      <c r="AK187" t="inlineStr"/>
+      <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="n">
+        <v>1351.707668354289</v>
+      </c>
+      <c r="AO187" t="inlineStr"/>
+      <c r="AP187" t="inlineStr"/>
+      <c r="AQ187" t="inlineStr"/>
+      <c r="AR187" t="inlineStr"/>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AU187" t="n">
+        <v>1264.864435918396</v>
+      </c>
+      <c r="AV187" t="inlineStr"/>
+      <c r="AW187" t="n">
+        <v>1306.870126178367</v>
+      </c>
+      <c r="AX187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr"/>
+      <c r="BA187" t="inlineStr"/>
+      <c r="BB187" t="inlineStr"/>
+      <c r="BC187" t="inlineStr"/>
+      <c r="BD187" t="inlineStr"/>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/elo_time_table.xlsx
+++ b/exports/elo_time_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF187"/>
+  <dimension ref="A1:BG215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,11 @@
       <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Victoria LastName</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Emily Allen</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,7 @@
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -854,6 +860,7 @@
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -924,6 +931,7 @@
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -994,6 +1002,7 @@
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1064,6 +1073,7 @@
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1134,6 +1144,7 @@
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1204,6 +1215,7 @@
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1274,6 +1286,7 @@
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1344,6 +1357,7 @@
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1414,6 +1428,7 @@
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1484,6 +1499,7 @@
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1554,6 +1570,7 @@
       <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1624,6 +1641,7 @@
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1694,6 +1712,7 @@
       <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1760,6 +1779,7 @@
       <c r="BD16" t="inlineStr"/>
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1826,6 +1846,7 @@
       <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1892,6 +1913,7 @@
       <c r="BD18" t="inlineStr"/>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1958,6 +1980,7 @@
       <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2024,6 +2047,7 @@
       <c r="BD20" t="inlineStr"/>
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2090,6 +2114,7 @@
       <c r="BD21" t="inlineStr"/>
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2156,6 +2181,7 @@
       <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2222,6 +2248,7 @@
       <c r="BD23" t="inlineStr"/>
       <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2288,6 +2315,7 @@
       <c r="BD24" t="inlineStr"/>
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2354,6 +2382,7 @@
       <c r="BD25" t="inlineStr"/>
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2420,6 +2449,7 @@
       <c r="BD26" t="inlineStr"/>
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2486,6 +2516,7 @@
       <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2552,6 +2583,7 @@
       <c r="BD28" t="inlineStr"/>
       <c r="BE28" t="inlineStr"/>
       <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2618,6 +2650,7 @@
       <c r="BD29" t="inlineStr"/>
       <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2684,6 +2717,7 @@
       <c r="BD30" t="inlineStr"/>
       <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2750,6 +2784,7 @@
       <c r="BD31" t="inlineStr"/>
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2816,6 +2851,7 @@
       <c r="BD32" t="inlineStr"/>
       <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2882,6 +2918,7 @@
       <c r="BD33" t="inlineStr"/>
       <c r="BE33" t="inlineStr"/>
       <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2948,6 +2985,7 @@
       <c r="BD34" t="inlineStr"/>
       <c r="BE34" t="inlineStr"/>
       <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3014,6 +3052,7 @@
       <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr"/>
       <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3080,6 +3119,7 @@
       <c r="BD36" t="inlineStr"/>
       <c r="BE36" t="inlineStr"/>
       <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3146,6 +3186,7 @@
       <c r="BD37" t="inlineStr"/>
       <c r="BE37" t="inlineStr"/>
       <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3212,6 +3253,7 @@
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="inlineStr"/>
       <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3278,6 +3320,7 @@
       <c r="BD39" t="inlineStr"/>
       <c r="BE39" t="inlineStr"/>
       <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3344,6 +3387,7 @@
       <c r="BD40" t="inlineStr"/>
       <c r="BE40" t="inlineStr"/>
       <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3410,6 +3454,7 @@
       <c r="BD41" t="inlineStr"/>
       <c r="BE41" t="inlineStr"/>
       <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3476,6 +3521,7 @@
       <c r="BD42" t="inlineStr"/>
       <c r="BE42" t="inlineStr"/>
       <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3542,6 +3588,7 @@
       <c r="BD43" t="inlineStr"/>
       <c r="BE43" t="inlineStr"/>
       <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3608,6 +3655,7 @@
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr"/>
       <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3678,6 +3726,7 @@
       <c r="BD45" t="inlineStr"/>
       <c r="BE45" t="inlineStr"/>
       <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3748,6 +3797,7 @@
       <c r="BD46" t="inlineStr"/>
       <c r="BE46" t="inlineStr"/>
       <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3818,6 +3868,7 @@
       <c r="BD47" t="inlineStr"/>
       <c r="BE47" t="inlineStr"/>
       <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3888,6 +3939,7 @@
       <c r="BD48" t="inlineStr"/>
       <c r="BE48" t="inlineStr"/>
       <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3958,6 +4010,7 @@
       <c r="BD49" t="inlineStr"/>
       <c r="BE49" t="inlineStr"/>
       <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4028,6 +4081,7 @@
       <c r="BD50" t="inlineStr"/>
       <c r="BE50" t="inlineStr"/>
       <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4098,6 +4152,7 @@
       <c r="BD51" t="inlineStr"/>
       <c r="BE51" t="inlineStr"/>
       <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -4168,6 +4223,7 @@
       <c r="BD52" t="inlineStr"/>
       <c r="BE52" t="inlineStr"/>
       <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4238,6 +4294,7 @@
       <c r="BD53" t="inlineStr"/>
       <c r="BE53" t="inlineStr"/>
       <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4308,6 +4365,7 @@
       <c r="BD54" t="inlineStr"/>
       <c r="BE54" t="inlineStr"/>
       <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4378,6 +4436,7 @@
       <c r="BD55" t="inlineStr"/>
       <c r="BE55" t="inlineStr"/>
       <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4448,6 +4507,7 @@
       <c r="BD56" t="inlineStr"/>
       <c r="BE56" t="inlineStr"/>
       <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4518,6 +4578,7 @@
       <c r="BD57" t="inlineStr"/>
       <c r="BE57" t="inlineStr"/>
       <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -4588,6 +4649,7 @@
       <c r="BD58" t="inlineStr"/>
       <c r="BE58" t="inlineStr"/>
       <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -4658,6 +4720,7 @@
       <c r="BD59" t="inlineStr"/>
       <c r="BE59" t="inlineStr"/>
       <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4728,6 +4791,7 @@
       <c r="BD60" t="inlineStr"/>
       <c r="BE60" t="inlineStr"/>
       <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4798,6 +4862,7 @@
       <c r="BD61" t="inlineStr"/>
       <c r="BE61" t="inlineStr"/>
       <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4864,6 +4929,7 @@
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
       <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4930,6 +4996,7 @@
       <c r="BD63" t="inlineStr"/>
       <c r="BE63" t="inlineStr"/>
       <c r="BF63" t="inlineStr"/>
+      <c r="BG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4996,6 +5063,7 @@
       <c r="BD64" t="inlineStr"/>
       <c r="BE64" t="inlineStr"/>
       <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -5062,6 +5130,7 @@
       <c r="BD65" t="inlineStr"/>
       <c r="BE65" t="inlineStr"/>
       <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -5128,6 +5197,7 @@
       <c r="BD66" t="inlineStr"/>
       <c r="BE66" t="inlineStr"/>
       <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -5194,6 +5264,7 @@
       <c r="BD67" t="inlineStr"/>
       <c r="BE67" t="inlineStr"/>
       <c r="BF67" t="inlineStr"/>
+      <c r="BG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5260,6 +5331,7 @@
       <c r="BD68" t="inlineStr"/>
       <c r="BE68" t="inlineStr"/>
       <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5326,6 +5398,7 @@
       <c r="BD69" t="inlineStr"/>
       <c r="BE69" t="inlineStr"/>
       <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -5392,6 +5465,7 @@
       <c r="BD70" t="inlineStr"/>
       <c r="BE70" t="inlineStr"/>
       <c r="BF70" t="inlineStr"/>
+      <c r="BG70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -5458,6 +5532,7 @@
       <c r="BD71" t="inlineStr"/>
       <c r="BE71" t="inlineStr"/>
       <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -5524,6 +5599,7 @@
       <c r="BD72" t="inlineStr"/>
       <c r="BE72" t="inlineStr"/>
       <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -5590,6 +5666,7 @@
       <c r="BD73" t="inlineStr"/>
       <c r="BE73" t="inlineStr"/>
       <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -5656,6 +5733,7 @@
       <c r="BD74" t="inlineStr"/>
       <c r="BE74" t="inlineStr"/>
       <c r="BF74" t="inlineStr"/>
+      <c r="BG74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -5722,6 +5800,7 @@
       <c r="BD75" t="inlineStr"/>
       <c r="BE75" t="inlineStr"/>
       <c r="BF75" t="inlineStr"/>
+      <c r="BG75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -5788,6 +5867,7 @@
       <c r="BD76" t="inlineStr"/>
       <c r="BE76" t="inlineStr"/>
       <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -5854,6 +5934,7 @@
       <c r="BD77" t="inlineStr"/>
       <c r="BE77" t="inlineStr"/>
       <c r="BF77" t="inlineStr"/>
+      <c r="BG77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5920,6 +6001,7 @@
       <c r="BD78" t="inlineStr"/>
       <c r="BE78" t="inlineStr"/>
       <c r="BF78" t="inlineStr"/>
+      <c r="BG78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -5986,6 +6068,7 @@
       <c r="BD79" t="inlineStr"/>
       <c r="BE79" t="inlineStr"/>
       <c r="BF79" t="inlineStr"/>
+      <c r="BG79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -6052,6 +6135,7 @@
       <c r="BD80" t="inlineStr"/>
       <c r="BE80" t="inlineStr"/>
       <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -6118,6 +6202,7 @@
       <c r="BD81" t="inlineStr"/>
       <c r="BE81" t="inlineStr"/>
       <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -6184,6 +6269,7 @@
       <c r="BD82" t="inlineStr"/>
       <c r="BE82" t="inlineStr"/>
       <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -6250,6 +6336,7 @@
       <c r="BD83" t="inlineStr"/>
       <c r="BE83" t="inlineStr"/>
       <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -6316,6 +6403,7 @@
       <c r="BD84" t="inlineStr"/>
       <c r="BE84" t="inlineStr"/>
       <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -6382,6 +6470,7 @@
       <c r="BD85" t="inlineStr"/>
       <c r="BE85" t="inlineStr"/>
       <c r="BF85" t="inlineStr"/>
+      <c r="BG85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -6448,6 +6537,7 @@
       <c r="BD86" t="inlineStr"/>
       <c r="BE86" t="inlineStr"/>
       <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -6514,6 +6604,7 @@
       <c r="BD87" t="inlineStr"/>
       <c r="BE87" t="inlineStr"/>
       <c r="BF87" t="inlineStr"/>
+      <c r="BG87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -6580,6 +6671,7 @@
       <c r="BD88" t="inlineStr"/>
       <c r="BE88" t="inlineStr"/>
       <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -6646,6 +6738,7 @@
       <c r="BD89" t="inlineStr"/>
       <c r="BE89" t="inlineStr"/>
       <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -6712,6 +6805,7 @@
       <c r="BD90" t="inlineStr"/>
       <c r="BE90" t="inlineStr"/>
       <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -6778,6 +6872,7 @@
       <c r="BD91" t="inlineStr"/>
       <c r="BE91" t="inlineStr"/>
       <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -6844,6 +6939,7 @@
       <c r="BD92" t="inlineStr"/>
       <c r="BE92" t="inlineStr"/>
       <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -6910,6 +7006,7 @@
       <c r="BD93" t="inlineStr"/>
       <c r="BE93" t="inlineStr"/>
       <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -6976,6 +7073,7 @@
       <c r="BD94" t="inlineStr"/>
       <c r="BE94" t="inlineStr"/>
       <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -7042,6 +7140,7 @@
       <c r="BD95" t="inlineStr"/>
       <c r="BE95" t="inlineStr"/>
       <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -7108,6 +7207,7 @@
       <c r="BD96" t="inlineStr"/>
       <c r="BE96" t="inlineStr"/>
       <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -7174,6 +7274,7 @@
       <c r="BD97" t="inlineStr"/>
       <c r="BE97" t="inlineStr"/>
       <c r="BF97" t="inlineStr"/>
+      <c r="BG97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -7240,6 +7341,7 @@
       <c r="BD98" t="inlineStr"/>
       <c r="BE98" t="inlineStr"/>
       <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -7310,6 +7412,7 @@
       <c r="BD99" t="inlineStr"/>
       <c r="BE99" t="inlineStr"/>
       <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -7380,6 +7483,7 @@
       <c r="BD100" t="inlineStr"/>
       <c r="BE100" t="inlineStr"/>
       <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -7450,6 +7554,7 @@
       <c r="BD101" t="inlineStr"/>
       <c r="BE101" t="inlineStr"/>
       <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -7520,6 +7625,7 @@
       <c r="BD102" t="inlineStr"/>
       <c r="BE102" t="inlineStr"/>
       <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -7590,6 +7696,7 @@
       <c r="BD103" t="inlineStr"/>
       <c r="BE103" t="inlineStr"/>
       <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -7660,6 +7767,7 @@
       <c r="BD104" t="inlineStr"/>
       <c r="BE104" t="inlineStr"/>
       <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -7730,6 +7838,7 @@
       <c r="BD105" t="inlineStr"/>
       <c r="BE105" t="inlineStr"/>
       <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -7800,6 +7909,7 @@
       <c r="BD106" t="inlineStr"/>
       <c r="BE106" t="inlineStr"/>
       <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -7870,6 +7980,7 @@
       <c r="BD107" t="inlineStr"/>
       <c r="BE107" t="inlineStr"/>
       <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -7940,6 +8051,7 @@
       <c r="BD108" t="inlineStr"/>
       <c r="BE108" t="inlineStr"/>
       <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -8010,6 +8122,7 @@
       <c r="BD109" t="inlineStr"/>
       <c r="BE109" t="inlineStr"/>
       <c r="BF109" t="inlineStr"/>
+      <c r="BG109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -8080,6 +8193,7 @@
       <c r="BD110" t="inlineStr"/>
       <c r="BE110" t="inlineStr"/>
       <c r="BF110" t="inlineStr"/>
+      <c r="BG110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -8150,6 +8264,7 @@
       <c r="BD111" t="inlineStr"/>
       <c r="BE111" t="inlineStr"/>
       <c r="BF111" t="inlineStr"/>
+      <c r="BG111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -8220,6 +8335,7 @@
       <c r="BD112" t="inlineStr"/>
       <c r="BE112" t="inlineStr"/>
       <c r="BF112" t="inlineStr"/>
+      <c r="BG112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -8286,6 +8402,7 @@
       <c r="BD113" t="inlineStr"/>
       <c r="BE113" t="inlineStr"/>
       <c r="BF113" t="inlineStr"/>
+      <c r="BG113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -8352,6 +8469,7 @@
       <c r="BD114" t="inlineStr"/>
       <c r="BE114" t="inlineStr"/>
       <c r="BF114" t="inlineStr"/>
+      <c r="BG114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -8418,6 +8536,7 @@
       <c r="BD115" t="inlineStr"/>
       <c r="BE115" t="inlineStr"/>
       <c r="BF115" t="inlineStr"/>
+      <c r="BG115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -8484,6 +8603,7 @@
       <c r="BD116" t="inlineStr"/>
       <c r="BE116" t="inlineStr"/>
       <c r="BF116" t="inlineStr"/>
+      <c r="BG116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -8550,6 +8670,7 @@
       <c r="BD117" t="inlineStr"/>
       <c r="BE117" t="inlineStr"/>
       <c r="BF117" t="inlineStr"/>
+      <c r="BG117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -8616,6 +8737,7 @@
       <c r="BD118" t="inlineStr"/>
       <c r="BE118" t="inlineStr"/>
       <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -8682,6 +8804,7 @@
       <c r="BD119" t="inlineStr"/>
       <c r="BE119" t="inlineStr"/>
       <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -8748,6 +8871,7 @@
       <c r="BD120" t="inlineStr"/>
       <c r="BE120" t="inlineStr"/>
       <c r="BF120" t="inlineStr"/>
+      <c r="BG120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -8814,6 +8938,7 @@
       <c r="BD121" t="inlineStr"/>
       <c r="BE121" t="inlineStr"/>
       <c r="BF121" t="inlineStr"/>
+      <c r="BG121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -8880,6 +9005,7 @@
       <c r="BD122" t="inlineStr"/>
       <c r="BE122" t="inlineStr"/>
       <c r="BF122" t="inlineStr"/>
+      <c r="BG122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -8946,6 +9072,7 @@
       <c r="BD123" t="inlineStr"/>
       <c r="BE123" t="inlineStr"/>
       <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -9012,6 +9139,7 @@
       <c r="BD124" t="inlineStr"/>
       <c r="BE124" t="inlineStr"/>
       <c r="BF124" t="inlineStr"/>
+      <c r="BG124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -9078,6 +9206,7 @@
       <c r="BD125" t="inlineStr"/>
       <c r="BE125" t="inlineStr"/>
       <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -9144,6 +9273,7 @@
       <c r="BD126" t="inlineStr"/>
       <c r="BE126" t="inlineStr"/>
       <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -9210,6 +9340,7 @@
       <c r="BD127" t="inlineStr"/>
       <c r="BE127" t="inlineStr"/>
       <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -9276,6 +9407,7 @@
       <c r="BD128" t="inlineStr"/>
       <c r="BE128" t="inlineStr"/>
       <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -9342,6 +9474,7 @@
       <c r="BD129" t="inlineStr"/>
       <c r="BE129" t="inlineStr"/>
       <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -9408,6 +9541,7 @@
       <c r="BD130" t="inlineStr"/>
       <c r="BE130" t="inlineStr"/>
       <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -9478,6 +9612,7 @@
       <c r="BD131" t="inlineStr"/>
       <c r="BE131" t="inlineStr"/>
       <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -9548,6 +9683,7 @@
       <c r="BD132" t="inlineStr"/>
       <c r="BE132" t="inlineStr"/>
       <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -9618,6 +9754,7 @@
       <c r="BD133" t="inlineStr"/>
       <c r="BE133" t="inlineStr"/>
       <c r="BF133" t="inlineStr"/>
+      <c r="BG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -9688,6 +9825,7 @@
       <c r="BD134" t="inlineStr"/>
       <c r="BE134" t="inlineStr"/>
       <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -9758,6 +9896,7 @@
       <c r="BD135" t="inlineStr"/>
       <c r="BE135" t="inlineStr"/>
       <c r="BF135" t="inlineStr"/>
+      <c r="BG135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -9828,6 +9967,7 @@
       <c r="BD136" t="inlineStr"/>
       <c r="BE136" t="inlineStr"/>
       <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -9898,6 +10038,7 @@
       <c r="BD137" t="inlineStr"/>
       <c r="BE137" t="inlineStr"/>
       <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -9968,6 +10109,7 @@
       <c r="BD138" t="inlineStr"/>
       <c r="BE138" t="inlineStr"/>
       <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -10038,6 +10180,7 @@
       <c r="BD139" t="inlineStr"/>
       <c r="BE139" t="inlineStr"/>
       <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -10108,6 +10251,7 @@
       <c r="BD140" t="inlineStr"/>
       <c r="BE140" t="inlineStr"/>
       <c r="BF140" t="inlineStr"/>
+      <c r="BG140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -10178,6 +10322,7 @@
       <c r="BD141" t="inlineStr"/>
       <c r="BE141" t="inlineStr"/>
       <c r="BF141" t="inlineStr"/>
+      <c r="BG141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -10248,6 +10393,7 @@
       <c r="BD142" t="inlineStr"/>
       <c r="BE142" t="inlineStr"/>
       <c r="BF142" t="inlineStr"/>
+      <c r="BG142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -10314,6 +10460,7 @@
       <c r="BD143" t="inlineStr"/>
       <c r="BE143" t="inlineStr"/>
       <c r="BF143" t="inlineStr"/>
+      <c r="BG143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -10380,6 +10527,7 @@
       <c r="BD144" t="inlineStr"/>
       <c r="BE144" t="inlineStr"/>
       <c r="BF144" t="inlineStr"/>
+      <c r="BG144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -10446,6 +10594,7 @@
       <c r="BD145" t="inlineStr"/>
       <c r="BE145" t="inlineStr"/>
       <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -10512,6 +10661,7 @@
       <c r="BD146" t="inlineStr"/>
       <c r="BE146" t="inlineStr"/>
       <c r="BF146" t="inlineStr"/>
+      <c r="BG146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -10578,6 +10728,7 @@
       <c r="BD147" t="inlineStr"/>
       <c r="BE147" t="inlineStr"/>
       <c r="BF147" t="inlineStr"/>
+      <c r="BG147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -10644,6 +10795,7 @@
       <c r="BD148" t="inlineStr"/>
       <c r="BE148" t="inlineStr"/>
       <c r="BF148" t="inlineStr"/>
+      <c r="BG148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -10710,6 +10862,7 @@
       <c r="BD149" t="inlineStr"/>
       <c r="BE149" t="inlineStr"/>
       <c r="BF149" t="inlineStr"/>
+      <c r="BG149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -10776,6 +10929,7 @@
       <c r="BD150" t="inlineStr"/>
       <c r="BE150" t="inlineStr"/>
       <c r="BF150" t="inlineStr"/>
+      <c r="BG150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -10842,6 +10996,7 @@
       <c r="BD151" t="inlineStr"/>
       <c r="BE151" t="inlineStr"/>
       <c r="BF151" t="inlineStr"/>
+      <c r="BG151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -10908,6 +11063,7 @@
       <c r="BD152" t="inlineStr"/>
       <c r="BE152" t="inlineStr"/>
       <c r="BF152" t="inlineStr"/>
+      <c r="BG152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -10974,6 +11130,7 @@
       <c r="BD153" t="inlineStr"/>
       <c r="BE153" t="inlineStr"/>
       <c r="BF153" t="inlineStr"/>
+      <c r="BG153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -11040,6 +11197,7 @@
       <c r="BD154" t="inlineStr"/>
       <c r="BE154" t="inlineStr"/>
       <c r="BF154" t="inlineStr"/>
+      <c r="BG154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -11106,6 +11264,7 @@
       <c r="BD155" t="inlineStr"/>
       <c r="BE155" t="inlineStr"/>
       <c r="BF155" t="inlineStr"/>
+      <c r="BG155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -11172,6 +11331,7 @@
       <c r="BD156" t="inlineStr"/>
       <c r="BE156" t="inlineStr"/>
       <c r="BF156" t="inlineStr"/>
+      <c r="BG156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -11238,6 +11398,7 @@
       <c r="BD157" t="inlineStr"/>
       <c r="BE157" t="inlineStr"/>
       <c r="BF157" t="inlineStr"/>
+      <c r="BG157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -11304,6 +11465,7 @@
       <c r="BD158" t="inlineStr"/>
       <c r="BE158" t="inlineStr"/>
       <c r="BF158" t="inlineStr"/>
+      <c r="BG158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -11370,6 +11532,7 @@
       <c r="BD159" t="inlineStr"/>
       <c r="BE159" t="inlineStr"/>
       <c r="BF159" t="inlineStr"/>
+      <c r="BG159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -11436,6 +11599,7 @@
       <c r="BD160" t="inlineStr"/>
       <c r="BE160" t="inlineStr"/>
       <c r="BF160" t="inlineStr"/>
+      <c r="BG160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -11502,6 +11666,7 @@
       <c r="BD161" t="inlineStr"/>
       <c r="BE161" t="inlineStr"/>
       <c r="BF161" t="inlineStr"/>
+      <c r="BG161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -11568,6 +11733,7 @@
       <c r="BD162" t="inlineStr"/>
       <c r="BE162" t="inlineStr"/>
       <c r="BF162" t="inlineStr"/>
+      <c r="BG162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -11634,6 +11800,7 @@
       <c r="BD163" t="inlineStr"/>
       <c r="BE163" t="inlineStr"/>
       <c r="BF163" t="inlineStr"/>
+      <c r="BG163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -11700,6 +11867,7 @@
       <c r="BD164" t="inlineStr"/>
       <c r="BE164" t="inlineStr"/>
       <c r="BF164" t="inlineStr"/>
+      <c r="BG164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -11766,6 +11934,7 @@
       <c r="BD165" t="inlineStr"/>
       <c r="BE165" t="inlineStr"/>
       <c r="BF165" t="inlineStr"/>
+      <c r="BG165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -11832,6 +12001,7 @@
       <c r="BD166" t="inlineStr"/>
       <c r="BE166" t="inlineStr"/>
       <c r="BF166" t="inlineStr"/>
+      <c r="BG166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -11898,6 +12068,7 @@
       <c r="BD167" t="inlineStr"/>
       <c r="BE167" t="inlineStr"/>
       <c r="BF167" t="inlineStr"/>
+      <c r="BG167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -11964,6 +12135,7 @@
       <c r="BD168" t="inlineStr"/>
       <c r="BE168" t="inlineStr"/>
       <c r="BF168" t="inlineStr"/>
+      <c r="BG168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -12034,6 +12206,7 @@
       </c>
       <c r="BE169" t="inlineStr"/>
       <c r="BF169" t="inlineStr"/>
+      <c r="BG169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -12104,6 +12277,7 @@
       <c r="BF170" t="n">
         <v>1191.344785334807</v>
       </c>
+      <c r="BG170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -12174,6 +12348,7 @@
       <c r="BD171" t="inlineStr"/>
       <c r="BE171" t="inlineStr"/>
       <c r="BF171" t="inlineStr"/>
+      <c r="BG171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -12244,6 +12419,7 @@
       <c r="BD172" t="inlineStr"/>
       <c r="BE172" t="inlineStr"/>
       <c r="BF172" t="inlineStr"/>
+      <c r="BG172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -12314,6 +12490,7 @@
       </c>
       <c r="BE173" t="inlineStr"/>
       <c r="BF173" t="inlineStr"/>
+      <c r="BG173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -12384,6 +12561,7 @@
       <c r="BD174" t="inlineStr"/>
       <c r="BE174" t="inlineStr"/>
       <c r="BF174" t="inlineStr"/>
+      <c r="BG174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -12454,6 +12632,7 @@
         <v>1205.744701884857</v>
       </c>
       <c r="BF175" t="inlineStr"/>
+      <c r="BG175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -12524,6 +12703,7 @@
       <c r="BD176" t="inlineStr"/>
       <c r="BE176" t="inlineStr"/>
       <c r="BF176" t="inlineStr"/>
+      <c r="BG176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -12594,6 +12774,7 @@
         <v>1216.085497024427</v>
       </c>
       <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -12664,6 +12845,7 @@
       <c r="BD178" t="inlineStr"/>
       <c r="BE178" t="inlineStr"/>
       <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -12734,6 +12916,7 @@
       <c r="BD179" t="inlineStr"/>
       <c r="BE179" t="inlineStr"/>
       <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -12804,6 +12987,7 @@
       <c r="BD180" t="inlineStr"/>
       <c r="BE180" t="inlineStr"/>
       <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -12874,6 +13058,7 @@
       <c r="BD181" t="inlineStr"/>
       <c r="BE181" t="inlineStr"/>
       <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -12944,6 +13129,7 @@
         <v>1228.461710380021</v>
       </c>
       <c r="BF182" t="inlineStr"/>
+      <c r="BG182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -13014,6 +13200,7 @@
         <v>1179.079459106583</v>
       </c>
       <c r="BF183" t="inlineStr"/>
+      <c r="BG183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -13084,6 +13271,7 @@
       <c r="BD184" t="inlineStr"/>
       <c r="BE184" t="inlineStr"/>
       <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -13154,6 +13342,7 @@
       <c r="BD185" t="inlineStr"/>
       <c r="BE185" t="inlineStr"/>
       <c r="BF185" t="inlineStr"/>
+      <c r="BG185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -13224,6 +13413,7 @@
       <c r="BD186" t="inlineStr"/>
       <c r="BE186" t="inlineStr"/>
       <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -13294,6 +13484,1883 @@
       <c r="BD187" t="inlineStr"/>
       <c r="BE187" t="inlineStr"/>
       <c r="BF187" t="inlineStr"/>
+      <c r="BG187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="inlineStr"/>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="n">
+        <v>1216.305290505486</v>
+      </c>
+      <c r="AI188" t="inlineStr"/>
+      <c r="AJ188" t="inlineStr"/>
+      <c r="AK188" t="inlineStr"/>
+      <c r="AL188" t="inlineStr"/>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr"/>
+      <c r="AO188" t="inlineStr"/>
+      <c r="AP188" t="inlineStr"/>
+      <c r="AQ188" t="inlineStr"/>
+      <c r="AR188" t="inlineStr"/>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AU188" t="n">
+        <v>1274.433001908797</v>
+      </c>
+      <c r="AV188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr"/>
+      <c r="AX188" t="inlineStr"/>
+      <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr"/>
+      <c r="BA188" t="inlineStr"/>
+      <c r="BB188" t="inlineStr"/>
+      <c r="BC188" t="inlineStr"/>
+      <c r="BD188" t="inlineStr"/>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+      <c r="BG188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="n">
+        <v>998.1484359389061</v>
+      </c>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr"/>
+      <c r="AJ189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr"/>
+      <c r="AL189" t="n">
+        <v>1213.874945649285</v>
+      </c>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr"/>
+      <c r="AO189" t="inlineStr"/>
+      <c r="AP189" t="inlineStr"/>
+      <c r="AQ189" t="inlineStr"/>
+      <c r="AR189" t="inlineStr"/>
+      <c r="AS189" t="inlineStr"/>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AU189" t="inlineStr"/>
+      <c r="AV189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr"/>
+      <c r="AX189" t="inlineStr"/>
+      <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr"/>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+      <c r="BG189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="inlineStr"/>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr"/>
+      <c r="AJ190" t="inlineStr"/>
+      <c r="AK190" t="inlineStr"/>
+      <c r="AL190" t="inlineStr"/>
+      <c r="AM190" t="inlineStr"/>
+      <c r="AN190" t="inlineStr"/>
+      <c r="AO190" t="inlineStr"/>
+      <c r="AP190" t="inlineStr"/>
+      <c r="AQ190" t="inlineStr"/>
+      <c r="AR190" t="inlineStr"/>
+      <c r="AS190" t="inlineStr"/>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AU190" t="inlineStr"/>
+      <c r="AV190" t="n">
+        <v>1188.808981078968</v>
+      </c>
+      <c r="AW190" t="inlineStr"/>
+      <c r="AX190" t="inlineStr"/>
+      <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="n">
+        <v>1127.060891773698</v>
+      </c>
+      <c r="BA190" t="inlineStr"/>
+      <c r="BB190" t="inlineStr"/>
+      <c r="BC190" t="inlineStr"/>
+      <c r="BD190" t="inlineStr"/>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+      <c r="BG190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="n">
+        <v>1272.961125027073</v>
+      </c>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
+      <c r="AE191" t="inlineStr"/>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr"/>
+      <c r="AJ191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr"/>
+      <c r="AL191" t="inlineStr"/>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr"/>
+      <c r="AO191" t="inlineStr"/>
+      <c r="AP191" t="inlineStr"/>
+      <c r="AQ191" t="inlineStr"/>
+      <c r="AR191" t="inlineStr"/>
+      <c r="AS191" t="inlineStr"/>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AU191" t="inlineStr"/>
+      <c r="AV191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr"/>
+      <c r="AX191" t="inlineStr"/>
+      <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr"/>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="n">
+        <v>1179.255203420079</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr"/>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr"/>
+      <c r="AJ192" t="inlineStr"/>
+      <c r="AK192" t="inlineStr"/>
+      <c r="AL192" t="inlineStr"/>
+      <c r="AM192" t="inlineStr"/>
+      <c r="AN192" t="n">
+        <v>1351.572141346338</v>
+      </c>
+      <c r="AO192" t="inlineStr"/>
+      <c r="AP192" t="inlineStr"/>
+      <c r="AQ192" t="inlineStr"/>
+      <c r="AR192" t="inlineStr"/>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AU192" t="inlineStr"/>
+      <c r="AV192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr"/>
+      <c r="AX192" t="inlineStr"/>
+      <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr"/>
+      <c r="BA192" t="inlineStr"/>
+      <c r="BB192" t="inlineStr"/>
+      <c r="BC192" t="inlineStr"/>
+      <c r="BD192" t="n">
+        <v>1155.437178784734</v>
+      </c>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+      <c r="BG192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+      <c r="AE193" t="inlineStr"/>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr"/>
+      <c r="AJ193" t="inlineStr"/>
+      <c r="AK193" t="inlineStr"/>
+      <c r="AL193" t="inlineStr"/>
+      <c r="AM193" t="inlineStr"/>
+      <c r="AN193" t="inlineStr"/>
+      <c r="AO193" t="inlineStr"/>
+      <c r="AP193" t="inlineStr"/>
+      <c r="AQ193" t="inlineStr"/>
+      <c r="AR193" t="inlineStr"/>
+      <c r="AS193" t="inlineStr"/>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AU193" t="inlineStr"/>
+      <c r="AV193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr"/>
+      <c r="AX193" t="n">
+        <v>1108.587384291436</v>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr"/>
+      <c r="BA193" t="inlineStr"/>
+      <c r="BB193" t="inlineStr"/>
+      <c r="BC193" t="inlineStr"/>
+      <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="n">
+        <v>1199.988190734781</v>
+      </c>
+      <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="n">
+        <v>1247.429693541523</v>
+      </c>
+      <c r="AD194" t="inlineStr"/>
+      <c r="AE194" t="inlineStr"/>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr"/>
+      <c r="AJ194" t="inlineStr"/>
+      <c r="AK194" t="inlineStr"/>
+      <c r="AL194" t="inlineStr"/>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr"/>
+      <c r="AO194" t="inlineStr"/>
+      <c r="AP194" t="inlineStr"/>
+      <c r="AQ194" t="inlineStr"/>
+      <c r="AR194" t="inlineStr"/>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AU194" t="inlineStr"/>
+      <c r="AV194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr"/>
+      <c r="AX194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr"/>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="n">
+        <v>1182.827021428023</v>
+      </c>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="n">
+        <v>970.1571366894871</v>
+      </c>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr"/>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr"/>
+      <c r="AJ195" t="inlineStr"/>
+      <c r="AK195" t="inlineStr"/>
+      <c r="AL195" t="inlineStr"/>
+      <c r="AM195" t="inlineStr"/>
+      <c r="AN195" t="inlineStr"/>
+      <c r="AO195" t="inlineStr"/>
+      <c r="AP195" t="inlineStr"/>
+      <c r="AQ195" t="inlineStr"/>
+      <c r="AR195" t="inlineStr"/>
+      <c r="AS195" t="inlineStr"/>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AU195" t="inlineStr"/>
+      <c r="AV195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr"/>
+      <c r="AX195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="n">
+        <v>1155.052191023117</v>
+      </c>
+      <c r="BA195" t="inlineStr"/>
+      <c r="BB195" t="inlineStr"/>
+      <c r="BC195" t="inlineStr"/>
+      <c r="BD195" t="inlineStr"/>
+      <c r="BE195" t="inlineStr"/>
+      <c r="BF195" t="inlineStr"/>
+      <c r="BG195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr"/>
+      <c r="AJ196" t="inlineStr"/>
+      <c r="AK196" t="inlineStr"/>
+      <c r="AL196" t="inlineStr"/>
+      <c r="AM196" t="inlineStr"/>
+      <c r="AN196" t="inlineStr"/>
+      <c r="AO196" t="inlineStr"/>
+      <c r="AP196" t="inlineStr"/>
+      <c r="AQ196" t="inlineStr"/>
+      <c r="AR196" t="inlineStr"/>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AU196" t="inlineStr"/>
+      <c r="AV196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr"/>
+      <c r="AX196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr"/>
+      <c r="BA196" t="inlineStr"/>
+      <c r="BB196" t="inlineStr"/>
+      <c r="BC196" t="inlineStr"/>
+      <c r="BD196" t="n">
+        <v>1144.922813588369</v>
+      </c>
+      <c r="BE196" t="inlineStr"/>
+      <c r="BF196" t="inlineStr"/>
+      <c r="BG196" t="n">
+        <v>1189.769568616445</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr"/>
+      <c r="AJ197" t="inlineStr"/>
+      <c r="AK197" t="inlineStr"/>
+      <c r="AL197" t="inlineStr"/>
+      <c r="AM197" t="inlineStr"/>
+      <c r="AN197" t="inlineStr"/>
+      <c r="AO197" t="inlineStr"/>
+      <c r="AP197" t="inlineStr"/>
+      <c r="AQ197" t="inlineStr"/>
+      <c r="AR197" t="inlineStr"/>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AU197" t="inlineStr"/>
+      <c r="AV197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr"/>
+      <c r="AX197" t="n">
+        <v>1041.212316994321</v>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr"/>
+      <c r="BA197" t="inlineStr"/>
+      <c r="BB197" t="n">
+        <v>1250.202088725138</v>
+      </c>
+      <c r="BC197" t="inlineStr"/>
+      <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+      <c r="BG197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="n">
+        <v>1097.397427906869</v>
+      </c>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
+      <c r="AJ198" t="inlineStr"/>
+      <c r="AK198" t="inlineStr"/>
+      <c r="AL198" t="inlineStr"/>
+      <c r="AM198" t="inlineStr"/>
+      <c r="AN198" t="inlineStr"/>
+      <c r="AO198" t="inlineStr"/>
+      <c r="AP198" t="inlineStr"/>
+      <c r="AQ198" t="inlineStr"/>
+      <c r="AR198" t="inlineStr"/>
+      <c r="AS198" t="inlineStr"/>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AU198" t="n">
+        <v>1288.322680876291</v>
+      </c>
+      <c r="AV198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr"/>
+      <c r="AX198" t="inlineStr"/>
+      <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr"/>
+      <c r="BA198" t="inlineStr"/>
+      <c r="BB198" t="inlineStr"/>
+      <c r="BC198" t="inlineStr"/>
+      <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+      <c r="BG198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
+      <c r="AJ199" t="inlineStr"/>
+      <c r="AK199" t="inlineStr"/>
+      <c r="AL199" t="n">
+        <v>1248.311495213021</v>
+      </c>
+      <c r="AM199" t="inlineStr"/>
+      <c r="AN199" t="inlineStr"/>
+      <c r="AO199" t="inlineStr"/>
+      <c r="AP199" t="inlineStr"/>
+      <c r="AQ199" t="inlineStr"/>
+      <c r="AR199" t="inlineStr"/>
+      <c r="AS199" t="inlineStr"/>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AU199" t="inlineStr"/>
+      <c r="AV199" t="n">
+        <v>1154.372431515232</v>
+      </c>
+      <c r="AW199" t="inlineStr"/>
+      <c r="AX199" t="inlineStr"/>
+      <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr"/>
+      <c r="BA199" t="inlineStr"/>
+      <c r="BB199" t="inlineStr"/>
+      <c r="BC199" t="inlineStr"/>
+      <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+      <c r="BG199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="n">
+        <v>1265.857565993382</v>
+      </c>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
+      <c r="AJ200" t="inlineStr"/>
+      <c r="AK200" t="inlineStr"/>
+      <c r="AL200" t="inlineStr"/>
+      <c r="AM200" t="inlineStr"/>
+      <c r="AN200" t="n">
+        <v>1358.675700380029</v>
+      </c>
+      <c r="AO200" t="inlineStr"/>
+      <c r="AP200" t="inlineStr"/>
+      <c r="AQ200" t="inlineStr"/>
+      <c r="AR200" t="inlineStr"/>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AU200" t="inlineStr"/>
+      <c r="AV200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr"/>
+      <c r="AX200" t="inlineStr"/>
+      <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr"/>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="n">
+        <v>1256.471804300091</v>
+      </c>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
+      <c r="AJ201" t="inlineStr"/>
+      <c r="AK201" t="inlineStr"/>
+      <c r="AL201" t="inlineStr"/>
+      <c r="AM201" t="inlineStr"/>
+      <c r="AN201" t="inlineStr"/>
+      <c r="AO201" t="inlineStr"/>
+      <c r="AP201" t="inlineStr"/>
+      <c r="AQ201" t="inlineStr"/>
+      <c r="AR201" t="inlineStr"/>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AU201" t="inlineStr"/>
+      <c r="AV201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr"/>
+      <c r="AX201" t="inlineStr"/>
+      <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr"/>
+      <c r="BA201" t="inlineStr"/>
+      <c r="BB201" t="inlineStr"/>
+      <c r="BC201" t="inlineStr"/>
+      <c r="BD201" t="inlineStr"/>
+      <c r="BE201" t="n">
+        <v>1190.946079976213</v>
+      </c>
+      <c r="BF201" t="inlineStr"/>
+      <c r="BG201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="n">
+        <v>1094.874570005411</v>
+      </c>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="inlineStr"/>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr"/>
+      <c r="AJ202" t="inlineStr"/>
+      <c r="AK202" t="inlineStr"/>
+      <c r="AL202" t="inlineStr"/>
+      <c r="AM202" t="inlineStr"/>
+      <c r="AN202" t="inlineStr"/>
+      <c r="AO202" t="inlineStr"/>
+      <c r="AP202" t="inlineStr"/>
+      <c r="AQ202" t="inlineStr"/>
+      <c r="AR202" t="inlineStr"/>
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AU202" t="inlineStr"/>
+      <c r="AV202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr"/>
+      <c r="AX202" t="inlineStr"/>
+      <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr"/>
+      <c r="BA202" t="inlineStr"/>
+      <c r="BB202" t="n">
+        <v>1252.724946626596</v>
+      </c>
+      <c r="BC202" t="inlineStr"/>
+      <c r="BD202" t="inlineStr"/>
+      <c r="BE202" t="inlineStr"/>
+      <c r="BF202" t="inlineStr"/>
+      <c r="BG202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr"/>
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr"/>
+      <c r="AJ203" t="inlineStr"/>
+      <c r="AK203" t="inlineStr"/>
+      <c r="AL203" t="inlineStr"/>
+      <c r="AM203" t="inlineStr"/>
+      <c r="AN203" t="inlineStr"/>
+      <c r="AO203" t="inlineStr"/>
+      <c r="AP203" t="inlineStr"/>
+      <c r="AQ203" t="inlineStr"/>
+      <c r="AR203" t="inlineStr"/>
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AU203" t="inlineStr"/>
+      <c r="AV203" t="n">
+        <v>1192.579927751734</v>
+      </c>
+      <c r="AW203" t="inlineStr"/>
+      <c r="AX203" t="inlineStr"/>
+      <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr"/>
+      <c r="BA203" t="inlineStr"/>
+      <c r="BB203" t="inlineStr"/>
+      <c r="BC203" t="inlineStr"/>
+      <c r="BD203" t="inlineStr"/>
+      <c r="BE203" t="inlineStr"/>
+      <c r="BF203" t="inlineStr"/>
+      <c r="BG203" t="n">
+        <v>1151.562072379942</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="n">
+        <v>1306.966326334721</v>
+      </c>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="inlineStr"/>
+      <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr"/>
+      <c r="AJ204" t="inlineStr"/>
+      <c r="AK204" t="inlineStr"/>
+      <c r="AL204" t="inlineStr"/>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr"/>
+      <c r="AO204" t="inlineStr"/>
+      <c r="AP204" t="inlineStr"/>
+      <c r="AQ204" t="inlineStr"/>
+      <c r="AR204" t="inlineStr"/>
+      <c r="AS204" t="inlineStr"/>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AU204" t="inlineStr"/>
+      <c r="AV204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr"/>
+      <c r="AX204" t="inlineStr"/>
+      <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="n">
+        <v>1113.943430681777</v>
+      </c>
+      <c r="BA204" t="inlineStr"/>
+      <c r="BB204" t="inlineStr"/>
+      <c r="BC204" t="inlineStr"/>
+      <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+      <c r="BG204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="inlineStr"/>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="n">
+        <v>1250.723555161504</v>
+      </c>
+      <c r="AI205" t="inlineStr"/>
+      <c r="AJ205" t="inlineStr"/>
+      <c r="AK205" t="inlineStr"/>
+      <c r="AL205" t="inlineStr"/>
+      <c r="AM205" t="inlineStr"/>
+      <c r="AN205" t="inlineStr"/>
+      <c r="AO205" t="inlineStr"/>
+      <c r="AP205" t="inlineStr"/>
+      <c r="AQ205" t="inlineStr"/>
+      <c r="AR205" t="inlineStr"/>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AU205" t="inlineStr"/>
+      <c r="AV205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr"/>
+      <c r="AX205" t="inlineStr"/>
+      <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr"/>
+      <c r="BA205" t="inlineStr"/>
+      <c r="BB205" t="inlineStr"/>
+      <c r="BC205" t="inlineStr"/>
+      <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="n">
+        <v>1156.527815320195</v>
+      </c>
+      <c r="BF205" t="inlineStr"/>
+      <c r="BG205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+      <c r="AE206" t="inlineStr"/>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr"/>
+      <c r="AJ206" t="inlineStr"/>
+      <c r="AK206" t="inlineStr"/>
+      <c r="AL206" t="inlineStr"/>
+      <c r="AM206" t="inlineStr"/>
+      <c r="AN206" t="inlineStr"/>
+      <c r="AO206" t="inlineStr"/>
+      <c r="AP206" t="inlineStr"/>
+      <c r="AQ206" t="inlineStr"/>
+      <c r="AR206" t="inlineStr"/>
+      <c r="AS206" t="inlineStr"/>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AU206" t="inlineStr"/>
+      <c r="AV206" t="n">
+        <v>1220.328576577198</v>
+      </c>
+      <c r="AW206" t="inlineStr"/>
+      <c r="AX206" t="inlineStr"/>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr"/>
+      <c r="BA206" t="inlineStr"/>
+      <c r="BB206" t="n">
+        <v>1224.976297801132</v>
+      </c>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="n">
+        <v>1339.460494323347</v>
+      </c>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="inlineStr"/>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="n">
+        <v>1218.229387172878</v>
+      </c>
+      <c r="AI207" t="inlineStr"/>
+      <c r="AJ207" t="inlineStr"/>
+      <c r="AK207" t="inlineStr"/>
+      <c r="AL207" t="inlineStr"/>
+      <c r="AM207" t="inlineStr"/>
+      <c r="AN207" t="inlineStr"/>
+      <c r="AO207" t="inlineStr"/>
+      <c r="AP207" t="inlineStr"/>
+      <c r="AQ207" t="inlineStr"/>
+      <c r="AR207" t="inlineStr"/>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AU207" t="inlineStr"/>
+      <c r="AV207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr"/>
+      <c r="AX207" t="inlineStr"/>
+      <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr"/>
+      <c r="BA207" t="inlineStr"/>
+      <c r="BB207" t="inlineStr"/>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+      <c r="BG207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr"/>
+      <c r="AJ208" t="inlineStr"/>
+      <c r="AK208" t="inlineStr"/>
+      <c r="AL208" t="n">
+        <v>1214.806523429131</v>
+      </c>
+      <c r="AM208" t="inlineStr"/>
+      <c r="AN208" t="inlineStr"/>
+      <c r="AO208" t="inlineStr"/>
+      <c r="AP208" t="inlineStr"/>
+      <c r="AQ208" t="inlineStr"/>
+      <c r="AR208" t="inlineStr"/>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AU208" t="n">
+        <v>1321.827652660181</v>
+      </c>
+      <c r="AV208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr"/>
+      <c r="AX208" t="inlineStr"/>
+      <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr"/>
+      <c r="BA208" t="inlineStr"/>
+      <c r="BB208" t="inlineStr"/>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="n">
+        <v>1226.831001661494</v>
+      </c>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr"/>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr"/>
+      <c r="AJ209" t="inlineStr"/>
+      <c r="AK209" t="inlineStr"/>
+      <c r="AL209" t="inlineStr"/>
+      <c r="AM209" t="inlineStr"/>
+      <c r="AN209" t="n">
+        <v>1388.316503018625</v>
+      </c>
+      <c r="AO209" t="inlineStr"/>
+      <c r="AP209" t="inlineStr"/>
+      <c r="AQ209" t="inlineStr"/>
+      <c r="AR209" t="inlineStr"/>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AU209" t="inlineStr"/>
+      <c r="AV209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr"/>
+      <c r="AX209" t="inlineStr"/>
+      <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr"/>
+      <c r="BA209" t="inlineStr"/>
+      <c r="BB209" t="inlineStr"/>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="n">
+        <v>1343.714271352697</v>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr"/>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr"/>
+      <c r="AJ210" t="inlineStr"/>
+      <c r="AK210" t="inlineStr"/>
+      <c r="AL210" t="n">
+        <v>1210.552746399781</v>
+      </c>
+      <c r="AM210" t="inlineStr"/>
+      <c r="AN210" t="inlineStr"/>
+      <c r="AO210" t="inlineStr"/>
+      <c r="AP210" t="inlineStr"/>
+      <c r="AQ210" t="inlineStr"/>
+      <c r="AR210" t="inlineStr"/>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AU210" t="inlineStr"/>
+      <c r="AV210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr"/>
+      <c r="AX210" t="inlineStr"/>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr"/>
+      <c r="BA210" t="inlineStr"/>
+      <c r="BB210" t="inlineStr"/>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="n">
+        <v>1202.425363568024</v>
+      </c>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
+      <c r="AJ211" t="inlineStr"/>
+      <c r="AK211" t="inlineStr"/>
+      <c r="AL211" t="inlineStr"/>
+      <c r="AM211" t="inlineStr"/>
+      <c r="AN211" t="inlineStr"/>
+      <c r="AO211" t="inlineStr"/>
+      <c r="AP211" t="inlineStr"/>
+      <c r="AQ211" t="inlineStr"/>
+      <c r="AR211" t="inlineStr"/>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AU211" t="inlineStr"/>
+      <c r="AV211" t="n">
+        <v>1244.734214670669</v>
+      </c>
+      <c r="AW211" t="inlineStr"/>
+      <c r="AX211" t="inlineStr"/>
+      <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr"/>
+      <c r="BA211" t="inlineStr"/>
+      <c r="BB211" t="inlineStr"/>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="n">
+        <v>1313.554667431601</v>
+      </c>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr"/>
+      <c r="AJ212" t="inlineStr"/>
+      <c r="AK212" t="inlineStr"/>
+      <c r="AL212" t="inlineStr"/>
+      <c r="AM212" t="inlineStr"/>
+      <c r="AN212" t="inlineStr"/>
+      <c r="AO212" t="inlineStr"/>
+      <c r="AP212" t="inlineStr"/>
+      <c r="AQ212" t="inlineStr"/>
+      <c r="AR212" t="inlineStr"/>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AU212" t="inlineStr"/>
+      <c r="AV212" t="n">
+        <v>1274.893818591765</v>
+      </c>
+      <c r="AW212" t="inlineStr"/>
+      <c r="AX212" t="inlineStr"/>
+      <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr"/>
+      <c r="BA212" t="inlineStr"/>
+      <c r="BB212" t="inlineStr"/>
+      <c r="BC212" t="inlineStr"/>
+      <c r="BD212" t="inlineStr"/>
+      <c r="BE212" t="inlineStr"/>
+      <c r="BF212" t="inlineStr"/>
+      <c r="BG212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr"/>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr"/>
+      <c r="AJ213" t="inlineStr"/>
+      <c r="AK213" t="inlineStr"/>
+      <c r="AL213" t="inlineStr"/>
+      <c r="AM213" t="inlineStr"/>
+      <c r="AN213" t="n">
+        <v>1408.17329504118</v>
+      </c>
+      <c r="AO213" t="inlineStr"/>
+      <c r="AP213" t="inlineStr"/>
+      <c r="AQ213" t="inlineStr"/>
+      <c r="AR213" t="inlineStr"/>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AU213" t="n">
+        <v>1301.970860637625</v>
+      </c>
+      <c r="AV213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr"/>
+      <c r="AX213" t="inlineStr"/>
+      <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr"/>
+      <c r="BA213" t="inlineStr"/>
+      <c r="BB213" t="inlineStr"/>
+      <c r="BC213" t="inlineStr"/>
+      <c r="BD213" t="inlineStr"/>
+      <c r="BE213" t="inlineStr"/>
+      <c r="BF213" t="inlineStr"/>
+      <c r="BG213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr"/>
+      <c r="AJ214" t="inlineStr"/>
+      <c r="AK214" t="inlineStr"/>
+      <c r="AL214" t="inlineStr"/>
+      <c r="AM214" t="inlineStr"/>
+      <c r="AN214" t="inlineStr"/>
+      <c r="AO214" t="inlineStr"/>
+      <c r="AP214" t="inlineStr"/>
+      <c r="AQ214" t="inlineStr"/>
+      <c r="AR214" t="inlineStr"/>
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AU214" t="n">
+        <v>1276.282016687553</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>1300.582662541837</v>
+      </c>
+      <c r="AW214" t="inlineStr"/>
+      <c r="AX214" t="inlineStr"/>
+      <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr"/>
+      <c r="BA214" t="inlineStr"/>
+      <c r="BB214" t="inlineStr"/>
+      <c r="BC214" t="inlineStr"/>
+      <c r="BD214" t="inlineStr"/>
+      <c r="BE214" t="inlineStr"/>
+      <c r="BF214" t="inlineStr"/>
+      <c r="BG214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
+      <c r="AJ215" t="inlineStr"/>
+      <c r="AK215" t="inlineStr"/>
+      <c r="AL215" t="inlineStr"/>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="n">
+        <v>1413.480816780976</v>
+      </c>
+      <c r="AO215" t="inlineStr"/>
+      <c r="AP215" t="inlineStr"/>
+      <c r="AQ215" t="inlineStr"/>
+      <c r="AR215" t="inlineStr"/>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AU215" t="inlineStr"/>
+      <c r="AV215" t="n">
+        <v>1295.275140802042</v>
+      </c>
+      <c r="AW215" t="inlineStr"/>
+      <c r="AX215" t="inlineStr"/>
+      <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr"/>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
